--- a/data/CL32-May.xlsx
+++ b/data/CL32-May.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adane\dm_tracker\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2BFDD98-37BE-47CF-B8D9-D3D10B6E6265}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0E27DCD-B8CF-489F-B7F8-F5E9BE9D72CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E19347DB-D799-4254-8840-4A1125816596}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="178">
   <si>
     <t>Activity ID</t>
   </si>
@@ -146,18 +146,6 @@
     <t>Mechanical Modelling</t>
   </si>
   <si>
-    <t xml:space="preserve">      FER-3D-1050</t>
-  </si>
-  <si>
-    <t>Network modelling (to be done by Arup)</t>
-  </si>
-  <si>
-    <t>21-May-26 A</t>
-  </si>
-  <si>
-    <t>5 Day lag added from when optioneering is complete to allow ARUP to complete modelling</t>
-  </si>
-  <si>
     <t xml:space="preserve">      FER-3D-1010</t>
   </si>
   <si>
@@ -303,21 +291,6 @@
   </si>
   <si>
     <t>27-Apr-26 A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        FER-MEC-1120</t>
-  </si>
-  <si>
-    <t>MAE Raised JMS-MAE-TQ-000044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        FER-MEC-1130</t>
-  </si>
-  <si>
-    <t>[GET] response to JMS-MAE-TQ-000044</t>
-  </si>
-  <si>
-    <t>12-May-26 A</t>
   </si>
   <si>
     <t xml:space="preserve">        FER-PRO-1010</t>
@@ -971,7 +944,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7FEB57D-8EA3-487D-B8BA-A49B4CD8571C}">
-  <dimension ref="A1:K75"/>
+  <dimension ref="A1:K72"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46.85546875" bestFit="1" customWidth="1"/>
@@ -1228,69 +1201,72 @@
       <c r="B9" t="s">
         <v>37</v>
       </c>
-      <c r="C9" t="s">
-        <v>38</v>
+      <c r="C9" s="1">
+        <v>46174</v>
+      </c>
+      <c r="D9" s="1">
+        <v>46185</v>
       </c>
       <c r="E9" s="1">
         <v>46143</v>
       </c>
+      <c r="F9" s="1">
+        <v>46157</v>
+      </c>
       <c r="G9">
-        <v>-13</v>
+        <v>-19</v>
+      </c>
+      <c r="H9">
+        <v>-7</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J9" s="2">
-        <v>1</v>
-      </c>
-      <c r="K9" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" t="s">
         <v>40</v>
       </c>
-      <c r="B10" t="s">
-        <v>41</v>
-      </c>
-      <c r="C10" s="1">
-        <v>46174</v>
-      </c>
-      <c r="D10" s="1">
-        <v>46185</v>
-      </c>
       <c r="E10" s="1">
-        <v>46143</v>
+        <v>46111</v>
       </c>
       <c r="F10" s="1">
-        <v>46157</v>
+        <v>46114</v>
       </c>
       <c r="G10">
-        <v>-19</v>
-      </c>
-      <c r="H10">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="I10">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J10" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" t="s">
         <v>42</v>
-      </c>
-      <c r="B11" t="s">
-        <v>43</v>
       </c>
       <c r="C11" t="s">
         <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E11" s="1">
         <v>46111</v>
@@ -1310,16 +1286,16 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B12" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s">
         <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E12" s="1">
         <v>46111</v>
@@ -1339,16 +1315,16 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B13" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C13" t="s">
         <v>20</v>
       </c>
       <c r="D13" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E13" s="1">
         <v>46111</v>
@@ -1368,45 +1344,51 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" s="1">
+        <v>46147</v>
+      </c>
+      <c r="G14">
+        <v>-17</v>
+      </c>
+      <c r="H14">
+        <v>-17</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14" s="2">
+        <v>0</v>
+      </c>
+      <c r="K14" t="s">
         <v>49</v>
-      </c>
-      <c r="B14" t="s">
-        <v>50</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="s">
-        <v>44</v>
-      </c>
-      <c r="E14" s="1">
-        <v>46111</v>
-      </c>
-      <c r="F14" s="1">
-        <v>46114</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14" s="2">
-        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" t="s">
         <v>51</v>
       </c>
-      <c r="B15" t="s">
-        <v>52</v>
-      </c>
-      <c r="D15" t="s">
-        <v>14</v>
+      <c r="C15" s="1">
+        <v>46174</v>
+      </c>
+      <c r="D15" s="1">
+        <v>46178</v>
+      </c>
+      <c r="E15" s="1">
+        <v>46148</v>
       </c>
       <c r="F15" s="1">
-        <v>46147</v>
+        <v>46154</v>
       </c>
       <c r="G15">
         <v>-17</v>
@@ -1415,33 +1397,30 @@
         <v>-17</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J15" s="2">
         <v>0</v>
-      </c>
-      <c r="K15" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B16" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C16" s="1">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="D16" s="1">
-        <v>46178</v>
+        <v>46185</v>
       </c>
       <c r="E16" s="1">
-        <v>46148</v>
+        <v>46155</v>
       </c>
       <c r="F16" s="1">
-        <v>46154</v>
+        <v>46161</v>
       </c>
       <c r="G16">
         <v>-17</v>
@@ -1458,31 +1437,31 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B17" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C17" s="1">
-        <v>46181</v>
+        <v>46188</v>
       </c>
       <c r="D17" s="1">
-        <v>46185</v>
+        <v>46199</v>
       </c>
       <c r="E17" s="1">
-        <v>46155</v>
+        <v>46162</v>
       </c>
       <c r="F17" s="1">
-        <v>46161</v>
+        <v>46176</v>
       </c>
       <c r="G17">
         <v>-17</v>
       </c>
       <c r="H17">
-        <v>-17</v>
+        <v>-12</v>
       </c>
       <c r="I17">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J17" s="2">
         <v>0</v>
@@ -1490,22 +1469,22 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B18" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C18" s="1">
-        <v>46188</v>
+        <v>46202</v>
       </c>
       <c r="D18" s="1">
-        <v>46199</v>
+        <v>46206</v>
       </c>
       <c r="E18" s="1">
-        <v>46162</v>
+        <v>46177</v>
       </c>
       <c r="F18" s="1">
-        <v>46176</v>
+        <v>46183</v>
       </c>
       <c r="G18">
         <v>-17</v>
@@ -1514,7 +1493,7 @@
         <v>-12</v>
       </c>
       <c r="I18">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J18" s="2">
         <v>0</v>
@@ -1522,54 +1501,51 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>59</v>
+      </c>
+      <c r="B19" t="s">
         <v>60</v>
       </c>
-      <c r="B19" t="s">
-        <v>61</v>
-      </c>
-      <c r="C19" s="1">
-        <v>46202</v>
-      </c>
-      <c r="D19" s="1">
-        <v>46206</v>
+      <c r="C19" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" t="s">
+        <v>40</v>
       </c>
       <c r="E19" s="1">
-        <v>46177</v>
+        <v>46111</v>
       </c>
       <c r="F19" s="1">
-        <v>46183</v>
+        <v>46114</v>
       </c>
       <c r="G19">
-        <v>-17</v>
-      </c>
-      <c r="H19">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="I19">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J19" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>61</v>
+      </c>
+      <c r="B20" t="s">
+        <v>62</v>
+      </c>
+      <c r="C20" t="s">
         <v>63</v>
       </c>
-      <c r="B20" t="s">
+      <c r="D20" t="s">
         <v>64</v>
       </c>
-      <c r="C20" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" t="s">
-        <v>44</v>
-      </c>
       <c r="E20" s="1">
-        <v>46111</v>
+        <v>46119</v>
       </c>
       <c r="F20" s="1">
-        <v>46114</v>
+        <v>46125</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -1595,10 +1571,10 @@
         <v>68</v>
       </c>
       <c r="E21" s="1">
-        <v>46119</v>
+        <v>46126</v>
       </c>
       <c r="F21" s="1">
-        <v>46125</v>
+        <v>46132</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -1624,13 +1600,13 @@
         <v>72</v>
       </c>
       <c r="E22" s="1">
-        <v>46126</v>
+        <v>46133</v>
       </c>
       <c r="F22" s="1">
-        <v>46132</v>
+        <v>46150</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -1649,107 +1625,107 @@
       <c r="C23" t="s">
         <v>75</v>
       </c>
-      <c r="D23" t="s">
-        <v>76</v>
+      <c r="D23" s="1">
+        <v>46174</v>
       </c>
       <c r="E23" s="1">
-        <v>46133</v>
+        <v>46153</v>
       </c>
       <c r="F23" s="1">
-        <v>46150</v>
+        <v>46157</v>
       </c>
       <c r="G23">
         <v>-10</v>
       </c>
+      <c r="H23">
+        <v>2</v>
+      </c>
       <c r="I23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" s="2">
-        <v>1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>76</v>
+      </c>
+      <c r="B24" t="s">
         <v>77</v>
       </c>
-      <c r="B24" t="s">
-        <v>78</v>
-      </c>
-      <c r="C24" t="s">
-        <v>79</v>
+      <c r="C24" s="1">
+        <v>46188</v>
       </c>
       <c r="D24" s="1">
-        <v>46174</v>
+        <v>46199</v>
       </c>
       <c r="E24" s="1">
-        <v>46153</v>
+        <v>46162</v>
       </c>
       <c r="F24" s="1">
-        <v>46157</v>
+        <v>46176</v>
       </c>
       <c r="G24">
-        <v>-10</v>
+        <v>-17</v>
       </c>
       <c r="H24">
-        <v>2</v>
+        <v>-17</v>
       </c>
       <c r="I24">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J24" s="2">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B25" t="s">
-        <v>81</v>
-      </c>
-      <c r="C25" s="1">
-        <v>46188</v>
-      </c>
-      <c r="D25" s="1">
-        <v>46199</v>
+        <v>79</v>
+      </c>
+      <c r="C25" t="s">
+        <v>20</v>
+      </c>
+      <c r="D25" t="s">
+        <v>11</v>
       </c>
       <c r="E25" s="1">
-        <v>46162</v>
+        <v>46111</v>
       </c>
       <c r="F25" s="1">
-        <v>46176</v>
+        <v>46122</v>
       </c>
       <c r="G25">
-        <v>-17</v>
-      </c>
-      <c r="H25">
-        <v>-17</v>
+        <v>0</v>
       </c>
       <c r="I25">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J25" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C26" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="D26" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="E26" s="1">
-        <v>46111</v>
+        <v>46125</v>
       </c>
       <c r="F26" s="1">
-        <v>46122</v>
+        <v>46136</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -1763,25 +1739,25 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>82</v>
+      </c>
+      <c r="B27" t="s">
+        <v>83</v>
+      </c>
+      <c r="C27" t="s">
         <v>84</v>
       </c>
-      <c r="B27" t="s">
-        <v>85</v>
-      </c>
-      <c r="C27" t="s">
-        <v>68</v>
-      </c>
       <c r="D27" t="s">
-        <v>29</v>
+        <v>72</v>
       </c>
       <c r="E27" s="1">
-        <v>46125</v>
+        <v>46139</v>
       </c>
       <c r="F27" s="1">
-        <v>46136</v>
+        <v>46153</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -1792,25 +1768,25 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>85</v>
+      </c>
+      <c r="B28" t="s">
         <v>86</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
+        <v>58</v>
+      </c>
+      <c r="D28" t="s">
         <v>87</v>
       </c>
-      <c r="C28" t="s">
-        <v>88</v>
-      </c>
-      <c r="D28" t="s">
-        <v>76</v>
-      </c>
       <c r="E28" s="1">
-        <v>46139</v>
+        <v>46104</v>
       </c>
       <c r="F28" s="1">
-        <v>46153</v>
+        <v>46129</v>
       </c>
       <c r="G28">
-        <v>-9</v>
+        <v>0</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -1821,13 +1797,25 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>88</v>
+      </c>
+      <c r="B29" t="s">
         <v>89</v>
       </c>
-      <c r="B29" t="s">
-        <v>90</v>
-      </c>
       <c r="C29" t="s">
-        <v>30</v>
+        <v>20</v>
+      </c>
+      <c r="D29" t="s">
+        <v>87</v>
+      </c>
+      <c r="E29" s="1">
+        <v>46111</v>
+      </c>
+      <c r="F29" s="1">
+        <v>46129</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -1838,13 +1826,25 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>90</v>
+      </c>
+      <c r="B30" t="s">
         <v>91</v>
       </c>
-      <c r="B30" t="s">
-        <v>92</v>
+      <c r="C30" t="s">
+        <v>68</v>
       </c>
       <c r="D30" t="s">
-        <v>93</v>
+        <v>29</v>
+      </c>
+      <c r="E30" s="1">
+        <v>46132</v>
+      </c>
+      <c r="F30" s="1">
+        <v>46136</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -1855,80 +1855,80 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B31" t="s">
-        <v>95</v>
-      </c>
-      <c r="C31" t="s">
-        <v>62</v>
-      </c>
-      <c r="D31" t="s">
-        <v>96</v>
+        <v>93</v>
+      </c>
+      <c r="C31" s="1">
+        <v>46202</v>
       </c>
       <c r="E31" s="1">
-        <v>46104</v>
-      </c>
-      <c r="F31" s="1">
-        <v>46129</v>
+        <v>46177</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>-17</v>
+      </c>
+      <c r="H31">
+        <v>-17</v>
       </c>
       <c r="I31">
         <v>0</v>
       </c>
       <c r="J31" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B32" t="s">
-        <v>98</v>
-      </c>
-      <c r="C32" t="s">
-        <v>20</v>
-      </c>
-      <c r="D32" t="s">
-        <v>96</v>
+        <v>95</v>
+      </c>
+      <c r="C32" s="1">
+        <v>46202</v>
+      </c>
+      <c r="D32" s="1">
+        <v>46213</v>
       </c>
       <c r="E32" s="1">
-        <v>46111</v>
+        <v>46177</v>
       </c>
       <c r="F32" s="1">
-        <v>46129</v>
+        <v>46190</v>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>-17</v>
+      </c>
+      <c r="H32">
+        <v>-17</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J32" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B33" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C33" t="s">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="D33" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="E33" s="1">
-        <v>46132</v>
+        <v>46097</v>
       </c>
       <c r="F33" s="1">
-        <v>46136</v>
+        <v>46101</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -1942,25 +1942,31 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B34" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C34" s="1">
-        <v>46202</v>
+        <v>46188</v>
+      </c>
+      <c r="D34" s="1">
+        <v>46192</v>
       </c>
       <c r="E34" s="1">
-        <v>46177</v>
+        <v>46162</v>
+      </c>
+      <c r="F34" s="1">
+        <v>46169</v>
       </c>
       <c r="G34">
         <v>-17</v>
       </c>
       <c r="H34">
-        <v>-17</v>
+        <v>21</v>
       </c>
       <c r="I34">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J34" s="2">
         <v>0</v>
@@ -1968,28 +1974,28 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B35" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C35" s="1">
-        <v>46202</v>
+        <v>46195</v>
       </c>
       <c r="D35" s="1">
-        <v>46213</v>
+        <v>46206</v>
       </c>
       <c r="E35" s="1">
-        <v>46177</v>
+        <v>46170</v>
       </c>
       <c r="F35" s="1">
-        <v>46190</v>
+        <v>46183</v>
       </c>
       <c r="G35">
         <v>-17</v>
       </c>
       <c r="H35">
-        <v>-17</v>
+        <v>21</v>
       </c>
       <c r="I35">
         <v>10</v>
@@ -2000,57 +2006,60 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B36" t="s">
-        <v>106</v>
-      </c>
-      <c r="C36" t="s">
-        <v>15</v>
-      </c>
-      <c r="D36" t="s">
-        <v>13</v>
+        <v>103</v>
+      </c>
+      <c r="C36" s="1">
+        <v>46216</v>
+      </c>
+      <c r="D36" s="1">
+        <v>46227</v>
       </c>
       <c r="E36" s="1">
-        <v>46097</v>
+        <v>46191</v>
       </c>
       <c r="F36" s="1">
-        <v>46101</v>
+        <v>46204</v>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>-17</v>
+      </c>
+      <c r="H36">
+        <v>-17</v>
       </c>
       <c r="I36">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J36" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B37" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C37" s="1">
-        <v>46188</v>
+        <v>46230</v>
       </c>
       <c r="D37" s="1">
-        <v>46192</v>
+        <v>46234</v>
       </c>
       <c r="E37" s="1">
-        <v>46162</v>
+        <v>46205</v>
       </c>
       <c r="F37" s="1">
-        <v>46169</v>
+        <v>46211</v>
       </c>
       <c r="G37">
         <v>-17</v>
       </c>
       <c r="H37">
-        <v>21</v>
+        <v>-17</v>
       </c>
       <c r="I37">
         <v>5</v>
@@ -2061,28 +2070,28 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B38" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C38" s="1">
-        <v>46195</v>
+        <v>46237</v>
       </c>
       <c r="D38" s="1">
-        <v>46206</v>
+        <v>46248</v>
       </c>
       <c r="E38" s="1">
-        <v>46170</v>
+        <v>46212</v>
       </c>
       <c r="F38" s="1">
-        <v>46183</v>
+        <v>46225</v>
       </c>
       <c r="G38">
         <v>-17</v>
       </c>
       <c r="H38">
-        <v>21</v>
+        <v>-17</v>
       </c>
       <c r="I38">
         <v>10</v>
@@ -2093,22 +2102,22 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B39" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C39" s="1">
-        <v>46216</v>
+        <v>46251</v>
       </c>
       <c r="D39" s="1">
-        <v>46227</v>
+        <v>46255</v>
       </c>
       <c r="E39" s="1">
-        <v>46191</v>
+        <v>46226</v>
       </c>
       <c r="F39" s="1">
-        <v>46204</v>
+        <v>46232</v>
       </c>
       <c r="G39">
         <v>-17</v>
@@ -2117,7 +2126,7 @@
         <v>-17</v>
       </c>
       <c r="I39">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J39" s="2">
         <v>0</v>
@@ -2125,31 +2134,31 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B40" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C40" s="1">
-        <v>46230</v>
+        <v>46216</v>
       </c>
       <c r="D40" s="1">
-        <v>46234</v>
+        <v>46224</v>
       </c>
       <c r="E40" s="1">
-        <v>46205</v>
+        <v>46191</v>
       </c>
       <c r="F40" s="1">
-        <v>46211</v>
+        <v>46199</v>
       </c>
       <c r="G40">
         <v>-17</v>
       </c>
       <c r="H40">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="I40">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J40" s="2">
         <v>0</v>
@@ -2157,31 +2166,31 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B41" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C41" s="1">
-        <v>46237</v>
+        <v>46225</v>
       </c>
       <c r="D41" s="1">
-        <v>46248</v>
+        <v>46231</v>
       </c>
       <c r="E41" s="1">
-        <v>46212</v>
+        <v>46202</v>
       </c>
       <c r="F41" s="1">
-        <v>46225</v>
+        <v>46206</v>
       </c>
       <c r="G41">
         <v>-17</v>
       </c>
       <c r="H41">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="I41">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J41" s="2">
         <v>0</v>
@@ -2189,28 +2198,28 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B42" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C42" s="1">
-        <v>46251</v>
+        <v>46232</v>
       </c>
       <c r="D42" s="1">
-        <v>46255</v>
+        <v>46238</v>
       </c>
       <c r="E42" s="1">
-        <v>46226</v>
+        <v>46209</v>
       </c>
       <c r="F42" s="1">
-        <v>46232</v>
+        <v>46213</v>
       </c>
       <c r="G42">
         <v>-17</v>
       </c>
       <c r="H42">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="I42">
         <v>5</v>
@@ -2221,22 +2230,22 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B43" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C43" s="1">
+        <v>46239</v>
+      </c>
+      <c r="D43" s="1">
+        <v>46245</v>
+      </c>
+      <c r="E43" s="1">
         <v>46216</v>
       </c>
-      <c r="D43" s="1">
-        <v>46224</v>
-      </c>
-      <c r="E43" s="1">
-        <v>46191</v>
-      </c>
       <c r="F43" s="1">
-        <v>46199</v>
+        <v>46220</v>
       </c>
       <c r="G43">
         <v>-17</v>
@@ -2245,7 +2254,7 @@
         <v>-16</v>
       </c>
       <c r="I43">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J43" s="2">
         <v>0</v>
@@ -2253,22 +2262,22 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B44" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C44" s="1">
-        <v>46225</v>
+        <v>46246</v>
       </c>
       <c r="D44" s="1">
-        <v>46231</v>
+        <v>46252</v>
       </c>
       <c r="E44" s="1">
-        <v>46202</v>
+        <v>46223</v>
       </c>
       <c r="F44" s="1">
-        <v>46206</v>
+        <v>46227</v>
       </c>
       <c r="G44">
         <v>-17</v>
@@ -2285,22 +2294,22 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B45" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C45" s="1">
-        <v>46232</v>
+        <v>46253</v>
       </c>
       <c r="D45" s="1">
-        <v>46238</v>
+        <v>46259</v>
       </c>
       <c r="E45" s="1">
-        <v>46209</v>
+        <v>46230</v>
       </c>
       <c r="F45" s="1">
-        <v>46213</v>
+        <v>46234</v>
       </c>
       <c r="G45">
         <v>-17</v>
@@ -2317,28 +2326,28 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B46" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C46" s="1">
-        <v>46239</v>
+        <v>46216</v>
       </c>
       <c r="D46" s="1">
-        <v>46245</v>
+        <v>46220</v>
       </c>
       <c r="E46" s="1">
-        <v>46216</v>
+        <v>46191</v>
       </c>
       <c r="F46" s="1">
-        <v>46220</v>
+        <v>46197</v>
       </c>
       <c r="G46">
         <v>-17</v>
       </c>
       <c r="H46">
-        <v>-16</v>
+        <v>11</v>
       </c>
       <c r="I46">
         <v>5</v>
@@ -2349,31 +2358,31 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B47" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C47" s="1">
-        <v>46246</v>
+        <v>46258</v>
       </c>
       <c r="D47" s="1">
-        <v>46252</v>
+        <v>46260</v>
       </c>
       <c r="E47" s="1">
-        <v>46223</v>
+        <v>46233</v>
       </c>
       <c r="F47" s="1">
-        <v>46227</v>
+        <v>46237</v>
       </c>
       <c r="G47">
         <v>-17</v>
       </c>
       <c r="H47">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="I47">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J47" s="2">
         <v>0</v>
@@ -2381,28 +2390,28 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B48" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C48" s="1">
-        <v>46253</v>
+        <v>46237</v>
       </c>
       <c r="D48" s="1">
-        <v>46259</v>
+        <v>46241</v>
       </c>
       <c r="E48" s="1">
-        <v>46230</v>
+        <v>46212</v>
       </c>
       <c r="F48" s="1">
-        <v>46234</v>
+        <v>46218</v>
       </c>
       <c r="G48">
         <v>-17</v>
       </c>
       <c r="H48">
-        <v>-16</v>
+        <v>-4</v>
       </c>
       <c r="I48">
         <v>5</v>
@@ -2413,31 +2422,31 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B49" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C49" s="1">
-        <v>46216</v>
+        <v>46174</v>
       </c>
       <c r="D49" s="1">
-        <v>46220</v>
+        <v>46174</v>
       </c>
       <c r="E49" s="1">
-        <v>46191</v>
+        <v>46154</v>
       </c>
       <c r="F49" s="1">
-        <v>46197</v>
+        <v>46154</v>
       </c>
       <c r="G49">
-        <v>-17</v>
+        <v>-12</v>
       </c>
       <c r="H49">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="I49">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J49" s="2">
         <v>0</v>
@@ -2445,31 +2454,31 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B50" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C50" s="1">
-        <v>46258</v>
+        <v>46174</v>
       </c>
       <c r="D50" s="1">
-        <v>46260</v>
+        <v>46183</v>
       </c>
       <c r="E50" s="1">
-        <v>46233</v>
+        <v>46155</v>
       </c>
       <c r="F50" s="1">
-        <v>46237</v>
+        <v>46169</v>
       </c>
       <c r="G50">
-        <v>-17</v>
+        <v>-10</v>
       </c>
       <c r="H50">
-        <v>-17</v>
+        <v>38</v>
       </c>
       <c r="I50">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J50" s="2">
         <v>0</v>
@@ -2477,31 +2486,31 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>134</v>
+      </c>
+      <c r="B51" t="s">
         <v>135</v>
       </c>
-      <c r="B51" t="s">
-        <v>136</v>
-      </c>
       <c r="C51" s="1">
-        <v>46237</v>
+        <v>46216</v>
       </c>
       <c r="D51" s="1">
-        <v>46241</v>
+        <v>46227</v>
       </c>
       <c r="E51" s="1">
-        <v>46212</v>
+        <v>46191</v>
       </c>
       <c r="F51" s="1">
-        <v>46218</v>
+        <v>46204</v>
       </c>
       <c r="G51">
         <v>-17</v>
       </c>
       <c r="H51">
-        <v>-4</v>
+        <v>6</v>
       </c>
       <c r="I51">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J51" s="2">
         <v>0</v>
@@ -2509,31 +2518,31 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B52" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C52" s="1">
-        <v>46174</v>
+        <v>46237</v>
       </c>
       <c r="D52" s="1">
-        <v>46174</v>
+        <v>46241</v>
       </c>
       <c r="E52" s="1">
-        <v>46154</v>
+        <v>46212</v>
       </c>
       <c r="F52" s="1">
-        <v>46154</v>
+        <v>46218</v>
       </c>
       <c r="G52">
-        <v>-12</v>
+        <v>-17</v>
       </c>
       <c r="H52">
-        <v>38</v>
+        <v>-4</v>
       </c>
       <c r="I52">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J52" s="2">
         <v>0</v>
@@ -2541,31 +2550,31 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B53" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C53" s="1">
-        <v>46174</v>
+        <v>46237</v>
       </c>
       <c r="D53" s="1">
-        <v>46183</v>
+        <v>46241</v>
       </c>
       <c r="E53" s="1">
-        <v>46155</v>
+        <v>46212</v>
       </c>
       <c r="F53" s="1">
-        <v>46169</v>
+        <v>46218</v>
       </c>
       <c r="G53">
-        <v>-10</v>
+        <v>-17</v>
       </c>
       <c r="H53">
-        <v>38</v>
+        <v>-4</v>
       </c>
       <c r="I53">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J53" s="2">
         <v>0</v>
@@ -2573,31 +2582,31 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B54" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C54" s="1">
         <v>46216</v>
       </c>
       <c r="D54" s="1">
-        <v>46227</v>
+        <v>46218</v>
       </c>
       <c r="E54" s="1">
         <v>46191</v>
       </c>
       <c r="F54" s="1">
-        <v>46204</v>
+        <v>46195</v>
       </c>
       <c r="G54">
         <v>-17</v>
       </c>
       <c r="H54">
-        <v>6</v>
+        <v>-11</v>
       </c>
       <c r="I54">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J54" s="2">
         <v>0</v>
@@ -2605,31 +2614,31 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B55" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C55" s="1">
-        <v>46237</v>
+        <v>46219</v>
       </c>
       <c r="D55" s="1">
-        <v>46241</v>
+        <v>46223</v>
       </c>
       <c r="E55" s="1">
-        <v>46212</v>
+        <v>46196</v>
       </c>
       <c r="F55" s="1">
-        <v>46218</v>
+        <v>46198</v>
       </c>
       <c r="G55">
         <v>-17</v>
       </c>
       <c r="H55">
-        <v>-4</v>
+        <v>-11</v>
       </c>
       <c r="I55">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J55" s="2">
         <v>0</v>
@@ -2637,31 +2646,31 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B56" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C56" s="1">
-        <v>46237</v>
+        <v>46224</v>
       </c>
       <c r="D56" s="1">
-        <v>46241</v>
+        <v>46226</v>
       </c>
       <c r="E56" s="1">
-        <v>46212</v>
+        <v>46199</v>
       </c>
       <c r="F56" s="1">
-        <v>46218</v>
+        <v>46203</v>
       </c>
       <c r="G56">
         <v>-17</v>
       </c>
       <c r="H56">
-        <v>-4</v>
+        <v>-11</v>
       </c>
       <c r="I56">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J56" s="2">
         <v>0</v>
@@ -2669,22 +2678,22 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B57" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C57" s="1">
-        <v>46216</v>
+        <v>46227</v>
       </c>
       <c r="D57" s="1">
-        <v>46218</v>
+        <v>46231</v>
       </c>
       <c r="E57" s="1">
-        <v>46191</v>
+        <v>46204</v>
       </c>
       <c r="F57" s="1">
-        <v>46195</v>
+        <v>46206</v>
       </c>
       <c r="G57">
         <v>-17</v>
@@ -2701,22 +2710,22 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B58" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C58" s="1">
-        <v>46219</v>
+        <v>46232</v>
       </c>
       <c r="D58" s="1">
-        <v>46223</v>
+        <v>46245</v>
       </c>
       <c r="E58" s="1">
-        <v>46196</v>
+        <v>46209</v>
       </c>
       <c r="F58" s="1">
-        <v>46198</v>
+        <v>46220</v>
       </c>
       <c r="G58">
         <v>-17</v>
@@ -2725,7 +2734,7 @@
         <v>-11</v>
       </c>
       <c r="I58">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J58" s="2">
         <v>0</v>
@@ -2733,28 +2742,28 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B59" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C59" s="1">
-        <v>46224</v>
+        <v>46232</v>
       </c>
       <c r="D59" s="1">
-        <v>46226</v>
+        <v>46234</v>
       </c>
       <c r="E59" s="1">
-        <v>46199</v>
+        <v>46209</v>
       </c>
       <c r="F59" s="1">
-        <v>46203</v>
+        <v>46211</v>
       </c>
       <c r="G59">
         <v>-17</v>
       </c>
       <c r="H59">
-        <v>-11</v>
+        <v>-4</v>
       </c>
       <c r="I59">
         <v>3</v>
@@ -2765,208 +2774,208 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B60" t="s">
-        <v>156</v>
-      </c>
-      <c r="C60" s="1">
-        <v>46227</v>
-      </c>
-      <c r="D60" s="1">
-        <v>46231</v>
+        <v>153</v>
+      </c>
+      <c r="C60" t="s">
+        <v>154</v>
+      </c>
+      <c r="D60" t="s">
+        <v>75</v>
       </c>
       <c r="E60" s="1">
-        <v>46204</v>
+        <v>46139</v>
       </c>
       <c r="F60" s="1">
-        <v>46206</v>
+        <v>46153</v>
       </c>
       <c r="G60">
-        <v>-17</v>
-      </c>
-      <c r="H60">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="I60">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J60" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B61" t="s">
-        <v>158</v>
-      </c>
-      <c r="C61" s="1">
-        <v>46232</v>
-      </c>
-      <c r="D61" s="1">
-        <v>46245</v>
+        <v>156</v>
+      </c>
+      <c r="C61" t="s">
+        <v>75</v>
+      </c>
+      <c r="D61" t="s">
+        <v>133</v>
       </c>
       <c r="E61" s="1">
-        <v>46209</v>
+        <v>46154</v>
       </c>
       <c r="F61" s="1">
-        <v>46220</v>
+        <v>46156</v>
       </c>
       <c r="G61">
-        <v>-17</v>
-      </c>
-      <c r="H61">
-        <v>-11</v>
+        <v>-9</v>
       </c>
       <c r="I61">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J61" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B62" t="s">
-        <v>160</v>
-      </c>
-      <c r="C62" s="1">
-        <v>46232</v>
+        <v>158</v>
+      </c>
+      <c r="C62" t="s">
+        <v>128</v>
       </c>
       <c r="D62" s="1">
-        <v>46234</v>
+        <v>46175</v>
       </c>
       <c r="E62" s="1">
-        <v>46209</v>
+        <v>46154</v>
       </c>
       <c r="F62" s="1">
-        <v>46211</v>
+        <v>46160</v>
       </c>
       <c r="G62">
-        <v>-17</v>
+        <v>-10</v>
       </c>
       <c r="H62">
-        <v>-4</v>
+        <v>31</v>
       </c>
       <c r="I62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J62" s="2">
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>159</v>
+      </c>
+      <c r="B63" t="s">
+        <v>160</v>
+      </c>
+      <c r="C63" t="s">
         <v>161</v>
       </c>
-      <c r="B63" t="s">
-        <v>162</v>
-      </c>
-      <c r="C63" t="s">
-        <v>163</v>
-      </c>
-      <c r="D63" t="s">
-        <v>79</v>
+      <c r="D63" s="1">
+        <v>46184</v>
       </c>
       <c r="E63" s="1">
-        <v>46139</v>
+        <v>46157</v>
       </c>
       <c r="F63" s="1">
-        <v>46153</v>
+        <v>46171</v>
       </c>
       <c r="G63">
-        <v>-10</v>
+        <v>-9</v>
+      </c>
+      <c r="H63">
+        <v>22</v>
       </c>
       <c r="I63">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J63" s="2">
-        <v>1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B64" t="s">
-        <v>165</v>
-      </c>
-      <c r="C64" t="s">
-        <v>79</v>
-      </c>
-      <c r="D64" t="s">
-        <v>142</v>
+        <v>163</v>
+      </c>
+      <c r="C64" s="1">
+        <v>46176</v>
+      </c>
+      <c r="D64" s="1">
+        <v>46178</v>
       </c>
       <c r="E64" s="1">
-        <v>46154</v>
+        <v>46161</v>
       </c>
       <c r="F64" s="1">
-        <v>46156</v>
+        <v>46163</v>
       </c>
       <c r="G64">
-        <v>-9</v>
+        <v>-10</v>
+      </c>
+      <c r="H64">
+        <v>31</v>
       </c>
       <c r="I64">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J64" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B65" t="s">
-        <v>167</v>
-      </c>
-      <c r="C65" t="s">
-        <v>137</v>
+        <v>165</v>
+      </c>
+      <c r="C65" s="1">
+        <v>46185</v>
       </c>
       <c r="D65" s="1">
-        <v>46175</v>
+        <v>46198</v>
       </c>
       <c r="E65" s="1">
-        <v>46154</v>
+        <v>46174</v>
       </c>
       <c r="F65" s="1">
-        <v>46160</v>
+        <v>46185</v>
       </c>
       <c r="G65">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="H65">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I65">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J65" s="2">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B66" t="s">
-        <v>169</v>
-      </c>
-      <c r="C66" t="s">
-        <v>170</v>
+        <v>167</v>
+      </c>
+      <c r="C66" s="1">
+        <v>46199</v>
       </c>
       <c r="D66" s="1">
-        <v>46184</v>
+        <v>46205</v>
       </c>
       <c r="E66" s="1">
-        <v>46157</v>
+        <v>46188</v>
       </c>
       <c r="F66" s="1">
-        <v>46171</v>
+        <v>46192</v>
       </c>
       <c r="G66">
         <v>-9</v>
@@ -2975,71 +2984,71 @@
         <v>22</v>
       </c>
       <c r="I66">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J66" s="2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B67" t="s">
-        <v>172</v>
-      </c>
-      <c r="C67" s="1">
-        <v>46176</v>
+        <v>169</v>
+      </c>
+      <c r="C67" t="s">
+        <v>161</v>
       </c>
       <c r="D67" s="1">
-        <v>46178</v>
+        <v>46177</v>
       </c>
       <c r="E67" s="1">
-        <v>46161</v>
+        <v>46157</v>
       </c>
       <c r="F67" s="1">
         <v>46163</v>
       </c>
       <c r="G67">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="H67">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I67">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J67" s="2">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B68" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C68" s="1">
+        <v>46181</v>
+      </c>
+      <c r="D68" s="1">
         <v>46185</v>
       </c>
-      <c r="D68" s="1">
-        <v>46198</v>
-      </c>
       <c r="E68" s="1">
-        <v>46174</v>
+        <v>46164</v>
       </c>
       <c r="F68" s="1">
-        <v>46185</v>
+        <v>46171</v>
       </c>
       <c r="G68">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H68">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="I68">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J68" s="2">
         <v>0</v>
@@ -3047,31 +3056,25 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B69" t="s">
-        <v>176</v>
+        <v>93</v>
       </c>
       <c r="C69" s="1">
-        <v>46199</v>
-      </c>
-      <c r="D69" s="1">
-        <v>46205</v>
+        <v>46261</v>
       </c>
       <c r="E69" s="1">
-        <v>46188</v>
-      </c>
-      <c r="F69" s="1">
-        <v>46192</v>
+        <v>46238</v>
       </c>
       <c r="G69">
-        <v>-9</v>
+        <v>-17</v>
       </c>
       <c r="H69">
-        <v>22</v>
+        <v>-17</v>
       </c>
       <c r="I69">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J69" s="2">
         <v>0</v>
@@ -3079,63 +3082,63 @@
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B70" t="s">
-        <v>178</v>
-      </c>
-      <c r="C70" t="s">
-        <v>170</v>
+        <v>95</v>
+      </c>
+      <c r="C70" s="1">
+        <v>46261</v>
       </c>
       <c r="D70" s="1">
-        <v>46177</v>
+        <v>46275</v>
       </c>
       <c r="E70" s="1">
-        <v>46157</v>
+        <v>46238</v>
       </c>
       <c r="F70" s="1">
-        <v>46163</v>
+        <v>46251</v>
       </c>
       <c r="G70">
-        <v>-9</v>
+        <v>-17</v>
       </c>
       <c r="H70">
-        <v>32</v>
+        <v>-17</v>
       </c>
       <c r="I70">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J70" s="2">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="B71" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="C71" s="1">
-        <v>46181</v>
+        <v>46276</v>
       </c>
       <c r="D71" s="1">
-        <v>46185</v>
+        <v>46289</v>
       </c>
       <c r="E71" s="1">
-        <v>46164</v>
+        <v>46252</v>
       </c>
       <c r="F71" s="1">
-        <v>46171</v>
+        <v>46266</v>
       </c>
       <c r="G71">
-        <v>-10</v>
+        <v>-17</v>
       </c>
       <c r="H71">
-        <v>31</v>
+        <v>-17</v>
       </c>
       <c r="I71">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J71" s="2">
         <v>0</v>
@@ -3143,16 +3146,16 @@
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="B72" t="s">
-        <v>102</v>
-      </c>
-      <c r="C72" s="1">
-        <v>46261</v>
-      </c>
-      <c r="E72" s="1">
-        <v>46238</v>
+        <v>177</v>
+      </c>
+      <c r="D72" s="1">
+        <v>46289</v>
+      </c>
+      <c r="F72" s="1">
+        <v>46266</v>
       </c>
       <c r="G72">
         <v>-17</v>
@@ -3164,96 +3167,6 @@
         <v>0</v>
       </c>
       <c r="J72" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>182</v>
-      </c>
-      <c r="B73" t="s">
-        <v>104</v>
-      </c>
-      <c r="C73" s="1">
-        <v>46261</v>
-      </c>
-      <c r="D73" s="1">
-        <v>46275</v>
-      </c>
-      <c r="E73" s="1">
-        <v>46238</v>
-      </c>
-      <c r="F73" s="1">
-        <v>46251</v>
-      </c>
-      <c r="G73">
-        <v>-17</v>
-      </c>
-      <c r="H73">
-        <v>-17</v>
-      </c>
-      <c r="I73">
-        <v>10</v>
-      </c>
-      <c r="J73" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>183</v>
-      </c>
-      <c r="B74" t="s">
-        <v>184</v>
-      </c>
-      <c r="C74" s="1">
-        <v>46276</v>
-      </c>
-      <c r="D74" s="1">
-        <v>46289</v>
-      </c>
-      <c r="E74" s="1">
-        <v>46252</v>
-      </c>
-      <c r="F74" s="1">
-        <v>46266</v>
-      </c>
-      <c r="G74">
-        <v>-17</v>
-      </c>
-      <c r="H74">
-        <v>-17</v>
-      </c>
-      <c r="I74">
-        <v>10</v>
-      </c>
-      <c r="J74" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>185</v>
-      </c>
-      <c r="B75" t="s">
-        <v>186</v>
-      </c>
-      <c r="D75" s="1">
-        <v>46289</v>
-      </c>
-      <c r="F75" s="1">
-        <v>46266</v>
-      </c>
-      <c r="G75">
-        <v>-17</v>
-      </c>
-      <c r="H75">
-        <v>-17</v>
-      </c>
-      <c r="I75">
-        <v>0</v>
-      </c>
-      <c r="J75" s="2">
         <v>0</v>
       </c>
     </row>

--- a/data/CL32-May.xlsx
+++ b/data/CL32-May.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adane\dm_tracker\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0E27DCD-B8CF-489F-B7F8-F5E9BE9D72CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E24A3F5-5E19-4E8C-B50D-F3E49AB8BF1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E19347DB-D799-4254-8840-4A1125816596}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="152">
   <si>
     <t>Activity ID</t>
   </si>
@@ -71,36 +71,12 @@
     <t>Comments</t>
   </si>
   <si>
-    <t>10-Apr-26 A</t>
-  </si>
-  <si>
-    <t>23-Apr-26 A</t>
-  </si>
-  <si>
-    <t>20-Mar-26 A</t>
-  </si>
-  <si>
-    <t>01-Jun-26*</t>
-  </si>
-  <si>
-    <t>16-Mar-26 A</t>
-  </si>
-  <si>
-    <t>29-Apr-26 A</t>
-  </si>
-  <si>
-    <t>13-May-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">      FER-CHA-1030</t>
   </si>
   <si>
     <t>Outfall pipework optioneering</t>
   </si>
   <si>
-    <t>30-Mar-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">      FER-3D-1020</t>
   </si>
   <si>
@@ -125,21 +101,12 @@
     <t>Civil Modelling - Tank</t>
   </si>
   <si>
-    <t>24-Apr-26 A</t>
-  </si>
-  <si>
-    <t>30-Apr-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">      FER-3D-1060</t>
   </si>
   <si>
     <t>Civil Modelling - Other Assets</t>
   </si>
   <si>
-    <t>01-May-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">      FER-3D-1070</t>
   </si>
   <si>
@@ -158,9 +125,6 @@
     <t>Determine entry/exit levels for pipework to and from overflow pipe</t>
   </si>
   <si>
-    <t>02-Apr-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">      FER-CSD-1010</t>
   </si>
   <si>
@@ -212,9 +176,6 @@
     <t>CAT2 check on MGE pile design</t>
   </si>
   <si>
-    <t>23-Mar-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">        FER-CIV-1000</t>
   </si>
   <si>
@@ -227,45 +188,24 @@
     <t>Outline drawing for connection into existing manhole on inlet pipe</t>
   </si>
   <si>
-    <t>07-Apr-26 A</t>
-  </si>
-  <si>
-    <t>13-Apr-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">        FER-CIV-1020</t>
   </si>
   <si>
     <t>GA &amp; Long sections of pipe entry/exit pipework from new MHs</t>
   </si>
   <si>
-    <t>14-Apr-26 A</t>
-  </si>
-  <si>
-    <t>20-Apr-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">        FER-CIV-1030</t>
   </si>
   <si>
     <t>Valve chamber standard detail drawing showing dimensions and layout</t>
   </si>
   <si>
-    <t>21-Apr-26 A</t>
-  </si>
-  <si>
-    <t>22-May-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">        FER-CIV-1040</t>
   </si>
   <si>
     <t>Kiosk slab proposal</t>
   </si>
   <si>
-    <t>26-May-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">        FER-CIV-1050</t>
   </si>
   <si>
@@ -290,18 +230,12 @@
     <t>Pump system curve and calcs with pump selection</t>
   </si>
   <si>
-    <t>27-Apr-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">        FER-PRO-1010</t>
   </si>
   <si>
     <t>Basis of Design</t>
   </si>
   <si>
-    <t>17-Apr-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">        FER-PRO-1000</t>
   </si>
   <si>
@@ -422,9 +356,6 @@
     <t>Routing &amp; Design</t>
   </si>
   <si>
-    <t>27-May-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">        FER-PRO-1030</t>
   </si>
   <si>
@@ -437,9 +368,6 @@
     <t>HAZOP &amp; ALM action and close out</t>
   </si>
   <si>
-    <t>28-May-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">          FER-MEC-1030</t>
   </si>
   <si>
@@ -500,9 +428,6 @@
     <t>User Requirement Specification</t>
   </si>
   <si>
-    <t>18-May-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">          FER-EICA-1020</t>
   </si>
   <si>
@@ -519,9 +444,6 @@
   </si>
   <si>
     <t>Power Supply Assessment</t>
-  </si>
-  <si>
-    <t>29-May-26 A</t>
   </si>
   <si>
     <t xml:space="preserve">          FER-EICA-1030</t>
@@ -576,6 +498,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -605,11 +530,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -949,9 +879,10 @@
   <cols>
     <col min="1" max="1" width="46.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="96.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.7109375" customWidth="1"/>
-    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="28.42578125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="35.28515625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="30.140625" style="3" customWidth="1"/>
     <col min="7" max="7" width="22.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16.7109375" bestFit="1" customWidth="1"/>
@@ -966,16 +897,16 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G1" t="s">
@@ -996,157 +927,159 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>17</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="C2" s="4">
+        <v>46141</v>
+      </c>
+      <c r="D2" s="4">
+        <v>46155</v>
+      </c>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
       <c r="I2">
         <v>0</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="1">
+        <v>14</v>
+      </c>
+      <c r="C3" s="4">
         <v>46111</v>
       </c>
-      <c r="F3" s="1">
+      <c r="D3" s="4">
         <v>46135</v>
       </c>
+      <c r="E3" s="4">
+        <v>46111</v>
+      </c>
+      <c r="F3" s="4">
+        <v>46135</v>
+      </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
-      <c r="J3" s="2">
+      <c r="J3" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="1">
+        <v>16</v>
+      </c>
+      <c r="C4" s="4">
         <v>46111</v>
       </c>
-      <c r="F4" s="1">
+      <c r="D4" s="4">
         <v>46135</v>
       </c>
+      <c r="E4" s="4">
+        <v>46111</v>
+      </c>
+      <c r="F4" s="4">
+        <v>46135</v>
+      </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
-      <c r="J4" s="2">
+      <c r="J4" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="1">
+        <v>18</v>
+      </c>
+      <c r="C5" s="4">
         <v>46122</v>
       </c>
-      <c r="F5" s="1">
+      <c r="D5" s="4">
         <v>46135</v>
       </c>
+      <c r="E5" s="4">
+        <v>46122</v>
+      </c>
+      <c r="F5" s="4">
+        <v>46135</v>
+      </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
-      <c r="J5" s="2">
+      <c r="J5" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="1">
+        <v>20</v>
+      </c>
+      <c r="C6" s="4">
         <v>46136</v>
       </c>
-      <c r="F6" s="1">
+      <c r="D6" s="4">
         <v>46142</v>
       </c>
+      <c r="E6" s="4">
+        <v>46136</v>
+      </c>
+      <c r="F6" s="4">
+        <v>46142</v>
+      </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
-      <c r="J6" s="2">
+      <c r="J6" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" s="1">
+        <v>22</v>
+      </c>
+      <c r="C7" s="4">
+        <v>46143</v>
+      </c>
+      <c r="D7" s="4">
         <v>46178</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="4">
         <v>46143</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F7" s="4">
         <v>46164</v>
       </c>
       <c r="G7">
@@ -1158,27 +1091,27 @@
       <c r="I7">
         <v>5</v>
       </c>
-      <c r="J7" s="3">
+      <c r="J7" s="2">
         <v>0.66669999999999996</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" s="1">
+        <v>24</v>
+      </c>
+      <c r="C8" s="4">
+        <v>46143</v>
+      </c>
+      <c r="D8" s="4">
         <v>46178</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="4">
         <v>46143</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8" s="4">
         <v>46164</v>
       </c>
       <c r="G8">
@@ -1190,27 +1123,27 @@
       <c r="I8">
         <v>5</v>
       </c>
-      <c r="J8" s="3">
+      <c r="J8" s="2">
         <v>0.66669999999999996</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" s="1">
+        <v>26</v>
+      </c>
+      <c r="C9" s="4">
         <v>46174</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" s="4">
         <v>46185</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" s="4">
         <v>46143</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F9" s="4">
         <v>46157</v>
       </c>
       <c r="G9">
@@ -1222,137 +1155,139 @@
       <c r="I9">
         <v>10</v>
       </c>
-      <c r="J9" s="2">
+      <c r="J9" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" t="s">
-        <v>40</v>
-      </c>
-      <c r="E10" s="1">
+        <v>28</v>
+      </c>
+      <c r="C10" s="4">
         <v>46111</v>
       </c>
-      <c r="F10" s="1">
+      <c r="D10" s="4">
         <v>46114</v>
       </c>
+      <c r="E10" s="4">
+        <v>46111</v>
+      </c>
+      <c r="F10" s="4">
+        <v>46114</v>
+      </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
-      <c r="J10" s="2">
+      <c r="J10" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
-      </c>
-      <c r="C11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" t="s">
-        <v>40</v>
-      </c>
-      <c r="E11" s="1">
+        <v>30</v>
+      </c>
+      <c r="C11" s="4">
         <v>46111</v>
       </c>
-      <c r="F11" s="1">
+      <c r="D11" s="4">
         <v>46114</v>
       </c>
+      <c r="E11" s="4">
+        <v>46111</v>
+      </c>
+      <c r="F11" s="4">
+        <v>46114</v>
+      </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
-      <c r="J11" s="2">
+      <c r="J11" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
-      </c>
-      <c r="C12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12" t="s">
-        <v>40</v>
-      </c>
-      <c r="E12" s="1">
+        <v>32</v>
+      </c>
+      <c r="C12" s="4">
         <v>46111</v>
       </c>
-      <c r="F12" s="1">
+      <c r="D12" s="4">
         <v>46114</v>
       </c>
+      <c r="E12" s="4">
+        <v>46111</v>
+      </c>
+      <c r="F12" s="4">
+        <v>46114</v>
+      </c>
       <c r="G12">
         <v>0</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
-      <c r="J12" s="2">
+      <c r="J12" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>46</v>
-      </c>
-      <c r="C13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D13" t="s">
-        <v>40</v>
-      </c>
-      <c r="E13" s="1">
+        <v>34</v>
+      </c>
+      <c r="C13" s="4">
         <v>46111</v>
       </c>
-      <c r="F13" s="1">
+      <c r="D13" s="4">
         <v>46114</v>
       </c>
+      <c r="E13" s="4">
+        <v>46111</v>
+      </c>
+      <c r="F13" s="4">
+        <v>46114</v>
+      </c>
       <c r="G13">
         <v>0</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
-      <c r="J13" s="2">
+      <c r="J13" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B14" t="s">
-        <v>48</v>
-      </c>
-      <c r="D14" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" s="1">
+        <v>36</v>
+      </c>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4">
+        <v>46174</v>
+      </c>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4">
         <v>46147</v>
       </c>
       <c r="G14">
@@ -1364,30 +1299,30 @@
       <c r="I14">
         <v>0</v>
       </c>
-      <c r="J14" s="2">
+      <c r="J14" s="1">
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="B15" t="s">
-        <v>51</v>
-      </c>
-      <c r="C15" s="1">
+        <v>39</v>
+      </c>
+      <c r="C15" s="4">
         <v>46174</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D15" s="4">
         <v>46178</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E15" s="4">
         <v>46148</v>
       </c>
-      <c r="F15" s="1">
+      <c r="F15" s="4">
         <v>46154</v>
       </c>
       <c r="G15">
@@ -1399,27 +1334,27 @@
       <c r="I15">
         <v>5</v>
       </c>
-      <c r="J15" s="2">
+      <c r="J15" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="B16" t="s">
-        <v>53</v>
-      </c>
-      <c r="C16" s="1">
+        <v>41</v>
+      </c>
+      <c r="C16" s="4">
         <v>46181</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D16" s="4">
         <v>46185</v>
       </c>
-      <c r="E16" s="1">
+      <c r="E16" s="4">
         <v>46155</v>
       </c>
-      <c r="F16" s="1">
+      <c r="F16" s="4">
         <v>46161</v>
       </c>
       <c r="G16">
@@ -1431,27 +1366,27 @@
       <c r="I16">
         <v>5</v>
       </c>
-      <c r="J16" s="2">
+      <c r="J16" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="B17" t="s">
-        <v>55</v>
-      </c>
-      <c r="C17" s="1">
+        <v>43</v>
+      </c>
+      <c r="C17" s="4">
         <v>46188</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D17" s="4">
         <v>46199</v>
       </c>
-      <c r="E17" s="1">
+      <c r="E17" s="4">
         <v>46162</v>
       </c>
-      <c r="F17" s="1">
+      <c r="F17" s="4">
         <v>46176</v>
       </c>
       <c r="G17">
@@ -1463,27 +1398,27 @@
       <c r="I17">
         <v>10</v>
       </c>
-      <c r="J17" s="2">
+      <c r="J17" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="B18" t="s">
-        <v>57</v>
-      </c>
-      <c r="C18" s="1">
+        <v>45</v>
+      </c>
+      <c r="C18" s="4">
         <v>46202</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D18" s="4">
         <v>46206</v>
       </c>
-      <c r="E18" s="1">
+      <c r="E18" s="4">
         <v>46177</v>
       </c>
-      <c r="F18" s="1">
+      <c r="F18" s="4">
         <v>46183</v>
       </c>
       <c r="G18">
@@ -1495,114 +1430,114 @@
       <c r="I18">
         <v>5</v>
       </c>
-      <c r="J18" s="2">
+      <c r="J18" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="B19" t="s">
-        <v>60</v>
-      </c>
-      <c r="C19" t="s">
-        <v>20</v>
-      </c>
-      <c r="D19" t="s">
-        <v>40</v>
-      </c>
-      <c r="E19" s="1">
+        <v>47</v>
+      </c>
+      <c r="C19" s="4">
         <v>46111</v>
       </c>
-      <c r="F19" s="1">
+      <c r="D19" s="4">
         <v>46114</v>
       </c>
+      <c r="E19" s="4">
+        <v>46111</v>
+      </c>
+      <c r="F19" s="4">
+        <v>46114</v>
+      </c>
       <c r="G19">
         <v>0</v>
       </c>
       <c r="I19">
         <v>0</v>
       </c>
-      <c r="J19" s="2">
+      <c r="J19" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="B20" t="s">
-        <v>62</v>
-      </c>
-      <c r="C20" t="s">
-        <v>63</v>
-      </c>
-      <c r="D20" t="s">
-        <v>64</v>
-      </c>
-      <c r="E20" s="1">
+        <v>49</v>
+      </c>
+      <c r="C20" s="4">
         <v>46119</v>
       </c>
-      <c r="F20" s="1">
+      <c r="D20" s="4">
         <v>46125</v>
       </c>
+      <c r="E20" s="4">
+        <v>46119</v>
+      </c>
+      <c r="F20" s="4">
+        <v>46125</v>
+      </c>
       <c r="G20">
         <v>0</v>
       </c>
       <c r="I20">
         <v>0</v>
       </c>
-      <c r="J20" s="2">
+      <c r="J20" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="B21" t="s">
-        <v>66</v>
-      </c>
-      <c r="C21" t="s">
-        <v>67</v>
-      </c>
-      <c r="D21" t="s">
-        <v>68</v>
-      </c>
-      <c r="E21" s="1">
+        <v>51</v>
+      </c>
+      <c r="C21" s="4">
         <v>46126</v>
       </c>
-      <c r="F21" s="1">
+      <c r="D21" s="4">
         <v>46132</v>
       </c>
+      <c r="E21" s="4">
+        <v>46126</v>
+      </c>
+      <c r="F21" s="4">
+        <v>46132</v>
+      </c>
       <c r="G21">
         <v>0</v>
       </c>
       <c r="I21">
         <v>0</v>
       </c>
-      <c r="J21" s="2">
+      <c r="J21" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="B22" t="s">
-        <v>70</v>
-      </c>
-      <c r="C22" t="s">
-        <v>71</v>
-      </c>
-      <c r="D22" t="s">
-        <v>72</v>
-      </c>
-      <c r="E22" s="1">
+        <v>53</v>
+      </c>
+      <c r="C22" s="4">
         <v>46133</v>
       </c>
-      <c r="F22" s="1">
+      <c r="D22" s="4">
+        <v>46164</v>
+      </c>
+      <c r="E22" s="4">
+        <v>46133</v>
+      </c>
+      <c r="F22" s="4">
         <v>46150</v>
       </c>
       <c r="G22">
@@ -1611,27 +1546,27 @@
       <c r="I22">
         <v>0</v>
       </c>
-      <c r="J22" s="2">
+      <c r="J22" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="B23" t="s">
-        <v>74</v>
-      </c>
-      <c r="C23" t="s">
-        <v>75</v>
-      </c>
-      <c r="D23" s="1">
+        <v>55</v>
+      </c>
+      <c r="C23" s="4">
+        <v>46168</v>
+      </c>
+      <c r="D23" s="4">
         <v>46174</v>
       </c>
-      <c r="E23" s="1">
+      <c r="E23" s="4">
         <v>46153</v>
       </c>
-      <c r="F23" s="1">
+      <c r="F23" s="4">
         <v>46157</v>
       </c>
       <c r="G23">
@@ -1643,27 +1578,27 @@
       <c r="I23">
         <v>1</v>
       </c>
-      <c r="J23" s="2">
+      <c r="J23" s="1">
         <v>0.8</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="B24" t="s">
-        <v>77</v>
-      </c>
-      <c r="C24" s="1">
+        <v>57</v>
+      </c>
+      <c r="C24" s="4">
         <v>46188</v>
       </c>
-      <c r="D24" s="1">
+      <c r="D24" s="4">
         <v>46199</v>
       </c>
-      <c r="E24" s="1">
+      <c r="E24" s="4">
         <v>46162</v>
       </c>
-      <c r="F24" s="1">
+      <c r="F24" s="4">
         <v>46176</v>
       </c>
       <c r="G24">
@@ -1675,85 +1610,85 @@
       <c r="I24">
         <v>10</v>
       </c>
-      <c r="J24" s="2">
+      <c r="J24" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="B25" t="s">
-        <v>79</v>
-      </c>
-      <c r="C25" t="s">
-        <v>20</v>
-      </c>
-      <c r="D25" t="s">
-        <v>11</v>
-      </c>
-      <c r="E25" s="1">
+        <v>59</v>
+      </c>
+      <c r="C25" s="4">
         <v>46111</v>
       </c>
-      <c r="F25" s="1">
+      <c r="D25" s="4">
         <v>46122</v>
       </c>
+      <c r="E25" s="4">
+        <v>46111</v>
+      </c>
+      <c r="F25" s="4">
+        <v>46122</v>
+      </c>
       <c r="G25">
         <v>0</v>
       </c>
       <c r="I25">
         <v>0</v>
       </c>
-      <c r="J25" s="2">
+      <c r="J25" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="B26" t="s">
-        <v>81</v>
-      </c>
-      <c r="C26" t="s">
-        <v>64</v>
-      </c>
-      <c r="D26" t="s">
-        <v>29</v>
-      </c>
-      <c r="E26" s="1">
+        <v>61</v>
+      </c>
+      <c r="C26" s="4">
         <v>46125</v>
       </c>
-      <c r="F26" s="1">
+      <c r="D26" s="4">
         <v>46136</v>
       </c>
+      <c r="E26" s="4">
+        <v>46125</v>
+      </c>
+      <c r="F26" s="4">
+        <v>46136</v>
+      </c>
       <c r="G26">
         <v>0</v>
       </c>
       <c r="I26">
         <v>0</v>
       </c>
-      <c r="J26" s="2">
+      <c r="J26" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="B27" t="s">
-        <v>83</v>
-      </c>
-      <c r="C27" t="s">
-        <v>84</v>
-      </c>
-      <c r="D27" t="s">
-        <v>72</v>
-      </c>
-      <c r="E27" s="1">
+        <v>63</v>
+      </c>
+      <c r="C27" s="4">
         <v>46139</v>
       </c>
-      <c r="F27" s="1">
+      <c r="D27" s="4">
+        <v>46164</v>
+      </c>
+      <c r="E27" s="4">
+        <v>46139</v>
+      </c>
+      <c r="F27" s="4">
         <v>46153</v>
       </c>
       <c r="G27">
@@ -1762,110 +1697,112 @@
       <c r="I27">
         <v>0</v>
       </c>
-      <c r="J27" s="2">
+      <c r="J27" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="B28" t="s">
-        <v>86</v>
-      </c>
-      <c r="C28" t="s">
-        <v>58</v>
-      </c>
-      <c r="D28" t="s">
-        <v>87</v>
-      </c>
-      <c r="E28" s="1">
+        <v>65</v>
+      </c>
+      <c r="C28" s="4">
         <v>46104</v>
       </c>
-      <c r="F28" s="1">
+      <c r="D28" s="4">
         <v>46129</v>
       </c>
+      <c r="E28" s="4">
+        <v>46104</v>
+      </c>
+      <c r="F28" s="4">
+        <v>46129</v>
+      </c>
       <c r="G28">
         <v>0</v>
       </c>
       <c r="I28">
         <v>0</v>
       </c>
-      <c r="J28" s="2">
+      <c r="J28" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="B29" t="s">
-        <v>89</v>
-      </c>
-      <c r="C29" t="s">
-        <v>20</v>
-      </c>
-      <c r="D29" t="s">
-        <v>87</v>
-      </c>
-      <c r="E29" s="1">
+        <v>67</v>
+      </c>
+      <c r="C29" s="4">
         <v>46111</v>
       </c>
-      <c r="F29" s="1">
+      <c r="D29" s="4">
         <v>46129</v>
       </c>
+      <c r="E29" s="4">
+        <v>46111</v>
+      </c>
+      <c r="F29" s="4">
+        <v>46129</v>
+      </c>
       <c r="G29">
         <v>0</v>
       </c>
       <c r="I29">
         <v>0</v>
       </c>
-      <c r="J29" s="2">
+      <c r="J29" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="B30" t="s">
-        <v>91</v>
-      </c>
-      <c r="C30" t="s">
-        <v>68</v>
-      </c>
-      <c r="D30" t="s">
-        <v>29</v>
-      </c>
-      <c r="E30" s="1">
+        <v>69</v>
+      </c>
+      <c r="C30" s="4">
         <v>46132</v>
       </c>
-      <c r="F30" s="1">
+      <c r="D30" s="4">
         <v>46136</v>
       </c>
+      <c r="E30" s="4">
+        <v>46132</v>
+      </c>
+      <c r="F30" s="4">
+        <v>46136</v>
+      </c>
       <c r="G30">
         <v>0</v>
       </c>
       <c r="I30">
         <v>0</v>
       </c>
-      <c r="J30" s="2">
+      <c r="J30" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="B31" t="s">
-        <v>93</v>
-      </c>
-      <c r="C31" s="1">
+        <v>71</v>
+      </c>
+      <c r="C31" s="4">
         <v>46202</v>
       </c>
-      <c r="E31" s="1">
+      <c r="D31" s="4"/>
+      <c r="E31" s="4">
         <v>46177</v>
       </c>
+      <c r="F31" s="4"/>
       <c r="G31">
         <v>-17</v>
       </c>
@@ -1875,27 +1812,27 @@
       <c r="I31">
         <v>0</v>
       </c>
-      <c r="J31" s="2">
+      <c r="J31" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="B32" t="s">
-        <v>95</v>
-      </c>
-      <c r="C32" s="1">
+        <v>73</v>
+      </c>
+      <c r="C32" s="4">
         <v>46202</v>
       </c>
-      <c r="D32" s="1">
+      <c r="D32" s="4">
         <v>46213</v>
       </c>
-      <c r="E32" s="1">
+      <c r="E32" s="4">
         <v>46177</v>
       </c>
-      <c r="F32" s="1">
+      <c r="F32" s="4">
         <v>46190</v>
       </c>
       <c r="G32">
@@ -1907,56 +1844,56 @@
       <c r="I32">
         <v>10</v>
       </c>
-      <c r="J32" s="2">
+      <c r="J32" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="B33" t="s">
-        <v>97</v>
-      </c>
-      <c r="C33" t="s">
-        <v>15</v>
-      </c>
-      <c r="D33" t="s">
-        <v>13</v>
-      </c>
-      <c r="E33" s="1">
+        <v>75</v>
+      </c>
+      <c r="C33" s="4">
         <v>46097</v>
       </c>
-      <c r="F33" s="1">
+      <c r="D33" s="4">
         <v>46101</v>
       </c>
+      <c r="E33" s="4">
+        <v>46097</v>
+      </c>
+      <c r="F33" s="4">
+        <v>46101</v>
+      </c>
       <c r="G33">
         <v>0</v>
       </c>
       <c r="I33">
         <v>0</v>
       </c>
-      <c r="J33" s="2">
+      <c r="J33" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="B34" t="s">
-        <v>99</v>
-      </c>
-      <c r="C34" s="1">
+        <v>77</v>
+      </c>
+      <c r="C34" s="4">
         <v>46188</v>
       </c>
-      <c r="D34" s="1">
+      <c r="D34" s="4">
         <v>46192</v>
       </c>
-      <c r="E34" s="1">
+      <c r="E34" s="4">
         <v>46162</v>
       </c>
-      <c r="F34" s="1">
+      <c r="F34" s="4">
         <v>46169</v>
       </c>
       <c r="G34">
@@ -1968,27 +1905,27 @@
       <c r="I34">
         <v>5</v>
       </c>
-      <c r="J34" s="2">
+      <c r="J34" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="B35" t="s">
-        <v>101</v>
-      </c>
-      <c r="C35" s="1">
+        <v>79</v>
+      </c>
+      <c r="C35" s="4">
         <v>46195</v>
       </c>
-      <c r="D35" s="1">
+      <c r="D35" s="4">
         <v>46206</v>
       </c>
-      <c r="E35" s="1">
+      <c r="E35" s="4">
         <v>46170</v>
       </c>
-      <c r="F35" s="1">
+      <c r="F35" s="4">
         <v>46183</v>
       </c>
       <c r="G35">
@@ -2000,27 +1937,27 @@
       <c r="I35">
         <v>10</v>
       </c>
-      <c r="J35" s="2">
+      <c r="J35" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="B36" t="s">
-        <v>103</v>
-      </c>
-      <c r="C36" s="1">
+        <v>81</v>
+      </c>
+      <c r="C36" s="4">
         <v>46216</v>
       </c>
-      <c r="D36" s="1">
+      <c r="D36" s="4">
         <v>46227</v>
       </c>
-      <c r="E36" s="1">
+      <c r="E36" s="4">
         <v>46191</v>
       </c>
-      <c r="F36" s="1">
+      <c r="F36" s="4">
         <v>46204</v>
       </c>
       <c r="G36">
@@ -2032,27 +1969,27 @@
       <c r="I36">
         <v>10</v>
       </c>
-      <c r="J36" s="2">
+      <c r="J36" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="B37" t="s">
-        <v>105</v>
-      </c>
-      <c r="C37" s="1">
+        <v>83</v>
+      </c>
+      <c r="C37" s="4">
         <v>46230</v>
       </c>
-      <c r="D37" s="1">
+      <c r="D37" s="4">
         <v>46234</v>
       </c>
-      <c r="E37" s="1">
+      <c r="E37" s="4">
         <v>46205</v>
       </c>
-      <c r="F37" s="1">
+      <c r="F37" s="4">
         <v>46211</v>
       </c>
       <c r="G37">
@@ -2064,27 +2001,27 @@
       <c r="I37">
         <v>5</v>
       </c>
-      <c r="J37" s="2">
+      <c r="J37" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="B38" t="s">
-        <v>107</v>
-      </c>
-      <c r="C38" s="1">
+        <v>85</v>
+      </c>
+      <c r="C38" s="4">
         <v>46237</v>
       </c>
-      <c r="D38" s="1">
+      <c r="D38" s="4">
         <v>46248</v>
       </c>
-      <c r="E38" s="1">
+      <c r="E38" s="4">
         <v>46212</v>
       </c>
-      <c r="F38" s="1">
+      <c r="F38" s="4">
         <v>46225</v>
       </c>
       <c r="G38">
@@ -2096,27 +2033,27 @@
       <c r="I38">
         <v>10</v>
       </c>
-      <c r="J38" s="2">
+      <c r="J38" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="B39" t="s">
-        <v>109</v>
-      </c>
-      <c r="C39" s="1">
+        <v>87</v>
+      </c>
+      <c r="C39" s="4">
         <v>46251</v>
       </c>
-      <c r="D39" s="1">
+      <c r="D39" s="4">
         <v>46255</v>
       </c>
-      <c r="E39" s="1">
+      <c r="E39" s="4">
         <v>46226</v>
       </c>
-      <c r="F39" s="1">
+      <c r="F39" s="4">
         <v>46232</v>
       </c>
       <c r="G39">
@@ -2128,27 +2065,27 @@
       <c r="I39">
         <v>5</v>
       </c>
-      <c r="J39" s="2">
+      <c r="J39" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="B40" t="s">
-        <v>111</v>
-      </c>
-      <c r="C40" s="1">
+        <v>89</v>
+      </c>
+      <c r="C40" s="4">
         <v>46216</v>
       </c>
-      <c r="D40" s="1">
+      <c r="D40" s="4">
         <v>46224</v>
       </c>
-      <c r="E40" s="1">
+      <c r="E40" s="4">
         <v>46191</v>
       </c>
-      <c r="F40" s="1">
+      <c r="F40" s="4">
         <v>46199</v>
       </c>
       <c r="G40">
@@ -2160,27 +2097,27 @@
       <c r="I40">
         <v>7</v>
       </c>
-      <c r="J40" s="2">
+      <c r="J40" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="B41" t="s">
-        <v>113</v>
-      </c>
-      <c r="C41" s="1">
+        <v>91</v>
+      </c>
+      <c r="C41" s="4">
         <v>46225</v>
       </c>
-      <c r="D41" s="1">
+      <c r="D41" s="4">
         <v>46231</v>
       </c>
-      <c r="E41" s="1">
+      <c r="E41" s="4">
         <v>46202</v>
       </c>
-      <c r="F41" s="1">
+      <c r="F41" s="4">
         <v>46206</v>
       </c>
       <c r="G41">
@@ -2192,27 +2129,27 @@
       <c r="I41">
         <v>5</v>
       </c>
-      <c r="J41" s="2">
+      <c r="J41" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="B42" t="s">
-        <v>115</v>
-      </c>
-      <c r="C42" s="1">
+        <v>93</v>
+      </c>
+      <c r="C42" s="4">
         <v>46232</v>
       </c>
-      <c r="D42" s="1">
+      <c r="D42" s="4">
         <v>46238</v>
       </c>
-      <c r="E42" s="1">
+      <c r="E42" s="4">
         <v>46209</v>
       </c>
-      <c r="F42" s="1">
+      <c r="F42" s="4">
         <v>46213</v>
       </c>
       <c r="G42">
@@ -2224,27 +2161,27 @@
       <c r="I42">
         <v>5</v>
       </c>
-      <c r="J42" s="2">
+      <c r="J42" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="B43" t="s">
-        <v>117</v>
-      </c>
-      <c r="C43" s="1">
+        <v>95</v>
+      </c>
+      <c r="C43" s="4">
         <v>46239</v>
       </c>
-      <c r="D43" s="1">
+      <c r="D43" s="4">
         <v>46245</v>
       </c>
-      <c r="E43" s="1">
+      <c r="E43" s="4">
         <v>46216</v>
       </c>
-      <c r="F43" s="1">
+      <c r="F43" s="4">
         <v>46220</v>
       </c>
       <c r="G43">
@@ -2256,27 +2193,27 @@
       <c r="I43">
         <v>5</v>
       </c>
-      <c r="J43" s="2">
+      <c r="J43" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="B44" t="s">
-        <v>119</v>
-      </c>
-      <c r="C44" s="1">
+        <v>97</v>
+      </c>
+      <c r="C44" s="4">
         <v>46246</v>
       </c>
-      <c r="D44" s="1">
+      <c r="D44" s="4">
         <v>46252</v>
       </c>
-      <c r="E44" s="1">
+      <c r="E44" s="4">
         <v>46223</v>
       </c>
-      <c r="F44" s="1">
+      <c r="F44" s="4">
         <v>46227</v>
       </c>
       <c r="G44">
@@ -2288,27 +2225,27 @@
       <c r="I44">
         <v>5</v>
       </c>
-      <c r="J44" s="2">
+      <c r="J44" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="B45" t="s">
-        <v>121</v>
-      </c>
-      <c r="C45" s="1">
+        <v>99</v>
+      </c>
+      <c r="C45" s="4">
         <v>46253</v>
       </c>
-      <c r="D45" s="1">
+      <c r="D45" s="4">
         <v>46259</v>
       </c>
-      <c r="E45" s="1">
+      <c r="E45" s="4">
         <v>46230</v>
       </c>
-      <c r="F45" s="1">
+      <c r="F45" s="4">
         <v>46234</v>
       </c>
       <c r="G45">
@@ -2320,27 +2257,27 @@
       <c r="I45">
         <v>5</v>
       </c>
-      <c r="J45" s="2">
+      <c r="J45" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="B46" t="s">
-        <v>123</v>
-      </c>
-      <c r="C46" s="1">
+        <v>101</v>
+      </c>
+      <c r="C46" s="4">
         <v>46216</v>
       </c>
-      <c r="D46" s="1">
+      <c r="D46" s="4">
         <v>46220</v>
       </c>
-      <c r="E46" s="1">
+      <c r="E46" s="4">
         <v>46191</v>
       </c>
-      <c r="F46" s="1">
+      <c r="F46" s="4">
         <v>46197</v>
       </c>
       <c r="G46">
@@ -2352,27 +2289,27 @@
       <c r="I46">
         <v>5</v>
       </c>
-      <c r="J46" s="2">
+      <c r="J46" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="B47" t="s">
-        <v>125</v>
-      </c>
-      <c r="C47" s="1">
+        <v>103</v>
+      </c>
+      <c r="C47" s="4">
         <v>46258</v>
       </c>
-      <c r="D47" s="1">
+      <c r="D47" s="4">
         <v>46260</v>
       </c>
-      <c r="E47" s="1">
+      <c r="E47" s="4">
         <v>46233</v>
       </c>
-      <c r="F47" s="1">
+      <c r="F47" s="4">
         <v>46237</v>
       </c>
       <c r="G47">
@@ -2384,27 +2321,27 @@
       <c r="I47">
         <v>3</v>
       </c>
-      <c r="J47" s="2">
+      <c r="J47" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="B48" t="s">
-        <v>127</v>
-      </c>
-      <c r="C48" s="1">
+        <v>105</v>
+      </c>
+      <c r="C48" s="4">
         <v>46237</v>
       </c>
-      <c r="D48" s="1">
+      <c r="D48" s="4">
         <v>46241</v>
       </c>
-      <c r="E48" s="1">
+      <c r="E48" s="4">
         <v>46212</v>
       </c>
-      <c r="F48" s="1">
+      <c r="F48" s="4">
         <v>46218</v>
       </c>
       <c r="G48">
@@ -2416,27 +2353,27 @@
       <c r="I48">
         <v>5</v>
       </c>
-      <c r="J48" s="2">
+      <c r="J48" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>129</v>
+        <v>106</v>
       </c>
       <c r="B49" t="s">
-        <v>130</v>
-      </c>
-      <c r="C49" s="1">
+        <v>107</v>
+      </c>
+      <c r="C49" s="4">
         <v>46174</v>
       </c>
-      <c r="D49" s="1">
+      <c r="D49" s="4">
         <v>46174</v>
       </c>
-      <c r="E49" s="1">
+      <c r="E49" s="4">
         <v>46154</v>
       </c>
-      <c r="F49" s="1">
+      <c r="F49" s="4">
         <v>46154</v>
       </c>
       <c r="G49">
@@ -2448,27 +2385,27 @@
       <c r="I49">
         <v>0</v>
       </c>
-      <c r="J49" s="2">
+      <c r="J49" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="B50" t="s">
-        <v>132</v>
-      </c>
-      <c r="C50" s="1">
+        <v>109</v>
+      </c>
+      <c r="C50" s="4">
         <v>46174</v>
       </c>
-      <c r="D50" s="1">
+      <c r="D50" s="4">
         <v>46183</v>
       </c>
-      <c r="E50" s="1">
+      <c r="E50" s="4">
         <v>46155</v>
       </c>
-      <c r="F50" s="1">
+      <c r="F50" s="4">
         <v>46169</v>
       </c>
       <c r="G50">
@@ -2480,27 +2417,27 @@
       <c r="I50">
         <v>8</v>
       </c>
-      <c r="J50" s="2">
+      <c r="J50" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="B51" t="s">
-        <v>135</v>
-      </c>
-      <c r="C51" s="1">
+        <v>111</v>
+      </c>
+      <c r="C51" s="4">
         <v>46216</v>
       </c>
-      <c r="D51" s="1">
+      <c r="D51" s="4">
         <v>46227</v>
       </c>
-      <c r="E51" s="1">
+      <c r="E51" s="4">
         <v>46191</v>
       </c>
-      <c r="F51" s="1">
+      <c r="F51" s="4">
         <v>46204</v>
       </c>
       <c r="G51">
@@ -2512,27 +2449,27 @@
       <c r="I51">
         <v>10</v>
       </c>
-      <c r="J51" s="2">
+      <c r="J51" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
       <c r="B52" t="s">
-        <v>137</v>
-      </c>
-      <c r="C52" s="1">
+        <v>113</v>
+      </c>
+      <c r="C52" s="4">
         <v>46237</v>
       </c>
-      <c r="D52" s="1">
+      <c r="D52" s="4">
         <v>46241</v>
       </c>
-      <c r="E52" s="1">
+      <c r="E52" s="4">
         <v>46212</v>
       </c>
-      <c r="F52" s="1">
+      <c r="F52" s="4">
         <v>46218</v>
       </c>
       <c r="G52">
@@ -2544,27 +2481,27 @@
       <c r="I52">
         <v>5</v>
       </c>
-      <c r="J52" s="2">
+      <c r="J52" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="B53" t="s">
-        <v>139</v>
-      </c>
-      <c r="C53" s="1">
+        <v>115</v>
+      </c>
+      <c r="C53" s="4">
         <v>46237</v>
       </c>
-      <c r="D53" s="1">
+      <c r="D53" s="4">
         <v>46241</v>
       </c>
-      <c r="E53" s="1">
+      <c r="E53" s="4">
         <v>46212</v>
       </c>
-      <c r="F53" s="1">
+      <c r="F53" s="4">
         <v>46218</v>
       </c>
       <c r="G53">
@@ -2576,27 +2513,27 @@
       <c r="I53">
         <v>5</v>
       </c>
-      <c r="J53" s="2">
+      <c r="J53" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>140</v>
+        <v>116</v>
       </c>
       <c r="B54" t="s">
-        <v>141</v>
-      </c>
-      <c r="C54" s="1">
+        <v>117</v>
+      </c>
+      <c r="C54" s="4">
         <v>46216</v>
       </c>
-      <c r="D54" s="1">
+      <c r="D54" s="4">
         <v>46218</v>
       </c>
-      <c r="E54" s="1">
+      <c r="E54" s="4">
         <v>46191</v>
       </c>
-      <c r="F54" s="1">
+      <c r="F54" s="4">
         <v>46195</v>
       </c>
       <c r="G54">
@@ -2608,27 +2545,27 @@
       <c r="I54">
         <v>3</v>
       </c>
-      <c r="J54" s="2">
+      <c r="J54" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="B55" t="s">
-        <v>143</v>
-      </c>
-      <c r="C55" s="1">
+        <v>119</v>
+      </c>
+      <c r="C55" s="4">
         <v>46219</v>
       </c>
-      <c r="D55" s="1">
+      <c r="D55" s="4">
         <v>46223</v>
       </c>
-      <c r="E55" s="1">
+      <c r="E55" s="4">
         <v>46196</v>
       </c>
-      <c r="F55" s="1">
+      <c r="F55" s="4">
         <v>46198</v>
       </c>
       <c r="G55">
@@ -2640,27 +2577,27 @@
       <c r="I55">
         <v>3</v>
       </c>
-      <c r="J55" s="2">
+      <c r="J55" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="B56" t="s">
-        <v>145</v>
-      </c>
-      <c r="C56" s="1">
+        <v>121</v>
+      </c>
+      <c r="C56" s="4">
         <v>46224</v>
       </c>
-      <c r="D56" s="1">
+      <c r="D56" s="4">
         <v>46226</v>
       </c>
-      <c r="E56" s="1">
+      <c r="E56" s="4">
         <v>46199</v>
       </c>
-      <c r="F56" s="1">
+      <c r="F56" s="4">
         <v>46203</v>
       </c>
       <c r="G56">
@@ -2672,27 +2609,27 @@
       <c r="I56">
         <v>3</v>
       </c>
-      <c r="J56" s="2">
+      <c r="J56" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="B57" t="s">
-        <v>147</v>
-      </c>
-      <c r="C57" s="1">
+        <v>123</v>
+      </c>
+      <c r="C57" s="4">
         <v>46227</v>
       </c>
-      <c r="D57" s="1">
+      <c r="D57" s="4">
         <v>46231</v>
       </c>
-      <c r="E57" s="1">
+      <c r="E57" s="4">
         <v>46204</v>
       </c>
-      <c r="F57" s="1">
+      <c r="F57" s="4">
         <v>46206</v>
       </c>
       <c r="G57">
@@ -2704,27 +2641,27 @@
       <c r="I57">
         <v>3</v>
       </c>
-      <c r="J57" s="2">
+      <c r="J57" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="B58" t="s">
-        <v>149</v>
-      </c>
-      <c r="C58" s="1">
+        <v>125</v>
+      </c>
+      <c r="C58" s="4">
         <v>46232</v>
       </c>
-      <c r="D58" s="1">
+      <c r="D58" s="4">
         <v>46245</v>
       </c>
-      <c r="E58" s="1">
+      <c r="E58" s="4">
         <v>46209</v>
       </c>
-      <c r="F58" s="1">
+      <c r="F58" s="4">
         <v>46220</v>
       </c>
       <c r="G58">
@@ -2736,27 +2673,27 @@
       <c r="I58">
         <v>10</v>
       </c>
-      <c r="J58" s="2">
+      <c r="J58" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>150</v>
+        <v>126</v>
       </c>
       <c r="B59" t="s">
-        <v>151</v>
-      </c>
-      <c r="C59" s="1">
+        <v>127</v>
+      </c>
+      <c r="C59" s="4">
         <v>46232</v>
       </c>
-      <c r="D59" s="1">
+      <c r="D59" s="4">
         <v>46234</v>
       </c>
-      <c r="E59" s="1">
+      <c r="E59" s="4">
         <v>46209</v>
       </c>
-      <c r="F59" s="1">
+      <c r="F59" s="4">
         <v>46211</v>
       </c>
       <c r="G59">
@@ -2768,27 +2705,27 @@
       <c r="I59">
         <v>3</v>
       </c>
-      <c r="J59" s="2">
+      <c r="J59" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="B60" t="s">
-        <v>153</v>
-      </c>
-      <c r="C60" t="s">
-        <v>154</v>
-      </c>
-      <c r="D60" t="s">
-        <v>75</v>
-      </c>
-      <c r="E60" s="1">
+        <v>129</v>
+      </c>
+      <c r="C60" s="4">
+        <v>46160</v>
+      </c>
+      <c r="D60" s="4">
+        <v>46168</v>
+      </c>
+      <c r="E60" s="4">
         <v>46139</v>
       </c>
-      <c r="F60" s="1">
+      <c r="F60" s="4">
         <v>46153</v>
       </c>
       <c r="G60">
@@ -2797,27 +2734,27 @@
       <c r="I60">
         <v>0</v>
       </c>
-      <c r="J60" s="2">
+      <c r="J60" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="B61" t="s">
-        <v>156</v>
-      </c>
-      <c r="C61" t="s">
-        <v>75</v>
-      </c>
-      <c r="D61" t="s">
-        <v>133</v>
-      </c>
-      <c r="E61" s="1">
+        <v>131</v>
+      </c>
+      <c r="C61" s="4">
+        <v>46168</v>
+      </c>
+      <c r="D61" s="4">
+        <v>46170</v>
+      </c>
+      <c r="E61" s="4">
         <v>46154</v>
       </c>
-      <c r="F61" s="1">
+      <c r="F61" s="4">
         <v>46156</v>
       </c>
       <c r="G61">
@@ -2826,27 +2763,27 @@
       <c r="I61">
         <v>0</v>
       </c>
-      <c r="J61" s="2">
+      <c r="J61" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="B62" t="s">
-        <v>158</v>
-      </c>
-      <c r="C62" t="s">
-        <v>128</v>
-      </c>
-      <c r="D62" s="1">
+        <v>133</v>
+      </c>
+      <c r="C62" s="4">
+        <v>46169</v>
+      </c>
+      <c r="D62" s="4">
         <v>46175</v>
       </c>
-      <c r="E62" s="1">
+      <c r="E62" s="4">
         <v>46154</v>
       </c>
-      <c r="F62" s="1">
+      <c r="F62" s="4">
         <v>46160</v>
       </c>
       <c r="G62">
@@ -2858,27 +2795,27 @@
       <c r="I62">
         <v>2</v>
       </c>
-      <c r="J62" s="2">
+      <c r="J62" s="1">
         <v>0.6</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>159</v>
+        <v>134</v>
       </c>
       <c r="B63" t="s">
-        <v>160</v>
-      </c>
-      <c r="C63" t="s">
-        <v>161</v>
-      </c>
-      <c r="D63" s="1">
+        <v>135</v>
+      </c>
+      <c r="C63" s="4">
+        <v>46171</v>
+      </c>
+      <c r="D63" s="4">
         <v>46184</v>
       </c>
-      <c r="E63" s="1">
+      <c r="E63" s="4">
         <v>46157</v>
       </c>
-      <c r="F63" s="1">
+      <c r="F63" s="4">
         <v>46171</v>
       </c>
       <c r="G63">
@@ -2890,27 +2827,27 @@
       <c r="I63">
         <v>9</v>
       </c>
-      <c r="J63" s="2">
+      <c r="J63" s="1">
         <v>0.1</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>162</v>
+        <v>136</v>
       </c>
       <c r="B64" t="s">
-        <v>163</v>
-      </c>
-      <c r="C64" s="1">
+        <v>137</v>
+      </c>
+      <c r="C64" s="4">
         <v>46176</v>
       </c>
-      <c r="D64" s="1">
+      <c r="D64" s="4">
         <v>46178</v>
       </c>
-      <c r="E64" s="1">
+      <c r="E64" s="4">
         <v>46161</v>
       </c>
-      <c r="F64" s="1">
+      <c r="F64" s="4">
         <v>46163</v>
       </c>
       <c r="G64">
@@ -2922,27 +2859,27 @@
       <c r="I64">
         <v>3</v>
       </c>
-      <c r="J64" s="2">
+      <c r="J64" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>164</v>
+        <v>138</v>
       </c>
       <c r="B65" t="s">
-        <v>165</v>
-      </c>
-      <c r="C65" s="1">
+        <v>139</v>
+      </c>
+      <c r="C65" s="4">
         <v>46185</v>
       </c>
-      <c r="D65" s="1">
+      <c r="D65" s="4">
         <v>46198</v>
       </c>
-      <c r="E65" s="1">
+      <c r="E65" s="4">
         <v>46174</v>
       </c>
-      <c r="F65" s="1">
+      <c r="F65" s="4">
         <v>46185</v>
       </c>
       <c r="G65">
@@ -2954,27 +2891,27 @@
       <c r="I65">
         <v>10</v>
       </c>
-      <c r="J65" s="2">
+      <c r="J65" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="B66" t="s">
-        <v>167</v>
-      </c>
-      <c r="C66" s="1">
+        <v>141</v>
+      </c>
+      <c r="C66" s="4">
         <v>46199</v>
       </c>
-      <c r="D66" s="1">
+      <c r="D66" s="4">
         <v>46205</v>
       </c>
-      <c r="E66" s="1">
+      <c r="E66" s="4">
         <v>46188</v>
       </c>
-      <c r="F66" s="1">
+      <c r="F66" s="4">
         <v>46192</v>
       </c>
       <c r="G66">
@@ -2986,27 +2923,27 @@
       <c r="I66">
         <v>5</v>
       </c>
-      <c r="J66" s="2">
+      <c r="J66" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>168</v>
+        <v>142</v>
       </c>
       <c r="B67" t="s">
-        <v>169</v>
-      </c>
-      <c r="C67" t="s">
-        <v>161</v>
-      </c>
-      <c r="D67" s="1">
+        <v>143</v>
+      </c>
+      <c r="C67" s="4">
+        <v>46171</v>
+      </c>
+      <c r="D67" s="4">
         <v>46177</v>
       </c>
-      <c r="E67" s="1">
+      <c r="E67" s="4">
         <v>46157</v>
       </c>
-      <c r="F67" s="1">
+      <c r="F67" s="4">
         <v>46163</v>
       </c>
       <c r="G67">
@@ -3018,27 +2955,27 @@
       <c r="I67">
         <v>4</v>
       </c>
-      <c r="J67" s="2">
+      <c r="J67" s="1">
         <v>0.2</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>170</v>
+        <v>144</v>
       </c>
       <c r="B68" t="s">
-        <v>171</v>
-      </c>
-      <c r="C68" s="1">
+        <v>145</v>
+      </c>
+      <c r="C68" s="4">
         <v>46181</v>
       </c>
-      <c r="D68" s="1">
+      <c r="D68" s="4">
         <v>46185</v>
       </c>
-      <c r="E68" s="1">
+      <c r="E68" s="4">
         <v>46164</v>
       </c>
-      <c r="F68" s="1">
+      <c r="F68" s="4">
         <v>46171</v>
       </c>
       <c r="G68">
@@ -3050,23 +2987,25 @@
       <c r="I68">
         <v>5</v>
       </c>
-      <c r="J68" s="2">
+      <c r="J68" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="B69" t="s">
-        <v>93</v>
-      </c>
-      <c r="C69" s="1">
+        <v>71</v>
+      </c>
+      <c r="C69" s="4">
         <v>46261</v>
       </c>
-      <c r="E69" s="1">
+      <c r="D69" s="4"/>
+      <c r="E69" s="4">
         <v>46238</v>
       </c>
+      <c r="F69" s="4"/>
       <c r="G69">
         <v>-17</v>
       </c>
@@ -3076,27 +3015,27 @@
       <c r="I69">
         <v>0</v>
       </c>
-      <c r="J69" s="2">
+      <c r="J69" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>173</v>
+        <v>147</v>
       </c>
       <c r="B70" t="s">
-        <v>95</v>
-      </c>
-      <c r="C70" s="1">
+        <v>73</v>
+      </c>
+      <c r="C70" s="4">
         <v>46261</v>
       </c>
-      <c r="D70" s="1">
+      <c r="D70" s="4">
         <v>46275</v>
       </c>
-      <c r="E70" s="1">
+      <c r="E70" s="4">
         <v>46238</v>
       </c>
-      <c r="F70" s="1">
+      <c r="F70" s="4">
         <v>46251</v>
       </c>
       <c r="G70">
@@ -3108,27 +3047,27 @@
       <c r="I70">
         <v>10</v>
       </c>
-      <c r="J70" s="2">
+      <c r="J70" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>174</v>
+        <v>148</v>
       </c>
       <c r="B71" t="s">
-        <v>175</v>
-      </c>
-      <c r="C71" s="1">
+        <v>149</v>
+      </c>
+      <c r="C71" s="4">
         <v>46276</v>
       </c>
-      <c r="D71" s="1">
+      <c r="D71" s="4">
         <v>46289</v>
       </c>
-      <c r="E71" s="1">
+      <c r="E71" s="4">
         <v>46252</v>
       </c>
-      <c r="F71" s="1">
+      <c r="F71" s="4">
         <v>46266</v>
       </c>
       <c r="G71">
@@ -3140,21 +3079,23 @@
       <c r="I71">
         <v>10</v>
       </c>
-      <c r="J71" s="2">
+      <c r="J71" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>176</v>
+        <v>150</v>
       </c>
       <c r="B72" t="s">
-        <v>177</v>
-      </c>
-      <c r="D72" s="1">
+        <v>151</v>
+      </c>
+      <c r="C72" s="4"/>
+      <c r="D72" s="4">
         <v>46289</v>
       </c>
-      <c r="F72" s="1">
+      <c r="E72" s="4"/>
+      <c r="F72" s="4">
         <v>46266</v>
       </c>
       <c r="G72">
@@ -3166,7 +3107,7 @@
       <c r="I72">
         <v>0</v>
       </c>
-      <c r="J72" s="2">
+      <c r="J72" s="1">
         <v>0</v>
       </c>
     </row>

--- a/data/CL32-May.xlsx
+++ b/data/CL32-May.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adane\dm_tracker\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E24A3F5-5E19-4E8C-B50D-F3E49AB8BF1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D853FD29-4164-4D99-A8C7-19795F02E78C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E19347DB-D799-4254-8840-4A1125816596}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="149">
   <si>
     <t>Activity ID</t>
   </si>
@@ -71,12 +71,6 @@
     <t>Comments</t>
   </si>
   <si>
-    <t xml:space="preserve">      FER-CHA-1030</t>
-  </si>
-  <si>
-    <t>Outfall pipework optioneering</t>
-  </si>
-  <si>
     <t xml:space="preserve">      FER-3D-1020</t>
   </si>
   <si>
@@ -246,9 +240,6 @@
   </si>
   <si>
     <t>Control Philosophy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        FER-REV-1000</t>
   </si>
   <si>
     <t>Submission of Outline Design Pack</t>
@@ -499,7 +490,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -537,7 +528,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -874,7 +865,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7FEB57D-8EA3-487D-B8BA-A49B4CD8571C}">
-  <dimension ref="A1:K72"/>
+  <dimension ref="A1:K70"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46.85546875" bestFit="1" customWidth="1"/>
@@ -933,13 +924,20 @@
         <v>12</v>
       </c>
       <c r="C2" s="4">
-        <v>46141</v>
+        <v>46111</v>
       </c>
       <c r="D2" s="4">
-        <v>46155</v>
-      </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
+        <v>46135</v>
+      </c>
+      <c r="E2" s="4">
+        <v>46111</v>
+      </c>
+      <c r="F2" s="4">
+        <v>46135</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
       <c r="I2">
         <v>0</v>
       </c>
@@ -984,13 +982,13 @@
         <v>16</v>
       </c>
       <c r="C4" s="4">
-        <v>46111</v>
+        <v>46122</v>
       </c>
       <c r="D4" s="4">
         <v>46135</v>
       </c>
       <c r="E4" s="4">
-        <v>46111</v>
+        <v>46122</v>
       </c>
       <c r="F4" s="4">
         <v>46135</v>
@@ -1013,16 +1011,16 @@
         <v>18</v>
       </c>
       <c r="C5" s="4">
-        <v>46122</v>
+        <v>46136</v>
       </c>
       <c r="D5" s="4">
-        <v>46135</v>
+        <v>46142</v>
       </c>
       <c r="E5" s="4">
-        <v>46122</v>
+        <v>46136</v>
       </c>
       <c r="F5" s="4">
-        <v>46135</v>
+        <v>46142</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1042,25 +1040,28 @@
         <v>20</v>
       </c>
       <c r="C6" s="4">
-        <v>46136</v>
+        <v>46143</v>
       </c>
       <c r="D6" s="4">
-        <v>46142</v>
+        <v>46178</v>
       </c>
       <c r="E6" s="4">
-        <v>46136</v>
+        <v>46143</v>
       </c>
       <c r="F6" s="4">
-        <v>46142</v>
+        <v>46164</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>-9</v>
+      </c>
+      <c r="H6">
+        <v>-17</v>
       </c>
       <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6" s="1">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0.66669999999999996</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -1103,28 +1104,28 @@
         <v>24</v>
       </c>
       <c r="C8" s="4">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="D8" s="4">
-        <v>46178</v>
+        <v>46185</v>
       </c>
       <c r="E8" s="4">
         <v>46143</v>
       </c>
       <c r="F8" s="4">
-        <v>46164</v>
+        <v>46157</v>
       </c>
       <c r="G8">
-        <v>-9</v>
+        <v>-19</v>
       </c>
       <c r="H8">
-        <v>-17</v>
+        <v>-7</v>
       </c>
       <c r="I8">
-        <v>5</v>
-      </c>
-      <c r="J8" s="2">
-        <v>0.66669999999999996</v>
+        <v>10</v>
+      </c>
+      <c r="J8" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -1135,28 +1136,25 @@
         <v>26</v>
       </c>
       <c r="C9" s="4">
-        <v>46174</v>
+        <v>46111</v>
       </c>
       <c r="D9" s="4">
-        <v>46185</v>
+        <v>46114</v>
       </c>
       <c r="E9" s="4">
-        <v>46143</v>
+        <v>46111</v>
       </c>
       <c r="F9" s="4">
-        <v>46157</v>
+        <v>46114</v>
       </c>
       <c r="G9">
-        <v>-19</v>
-      </c>
-      <c r="H9">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -1253,42 +1251,48 @@
       <c r="B13" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="4">
-        <v>46111</v>
-      </c>
+      <c r="C13" s="4"/>
       <c r="D13" s="4">
-        <v>46114</v>
-      </c>
-      <c r="E13" s="4">
-        <v>46111</v>
-      </c>
+        <v>46174</v>
+      </c>
+      <c r="E13" s="4"/>
       <c r="F13" s="4">
-        <v>46114</v>
+        <v>46147</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>-17</v>
+      </c>
+      <c r="H13">
+        <v>-17</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
       <c r="J13" s="1">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="K13" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" s="4"/>
+        <v>37</v>
+      </c>
+      <c r="C14" s="4">
+        <v>46174</v>
+      </c>
       <c r="D14" s="4">
-        <v>46174</v>
-      </c>
-      <c r="E14" s="4"/>
+        <v>46178</v>
+      </c>
+      <c r="E14" s="4">
+        <v>46148</v>
+      </c>
       <c r="F14" s="4">
-        <v>46147</v>
+        <v>46154</v>
       </c>
       <c r="G14">
         <v>-17</v>
@@ -1297,13 +1301,10 @@
         <v>-17</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J14" s="1">
         <v>0</v>
-      </c>
-      <c r="K14" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -1314,16 +1315,16 @@
         <v>39</v>
       </c>
       <c r="C15" s="4">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="D15" s="4">
-        <v>46178</v>
+        <v>46185</v>
       </c>
       <c r="E15" s="4">
-        <v>46148</v>
+        <v>46155</v>
       </c>
       <c r="F15" s="4">
-        <v>46154</v>
+        <v>46161</v>
       </c>
       <c r="G15">
         <v>-17</v>
@@ -1346,25 +1347,25 @@
         <v>41</v>
       </c>
       <c r="C16" s="4">
-        <v>46181</v>
+        <v>46188</v>
       </c>
       <c r="D16" s="4">
-        <v>46185</v>
+        <v>46199</v>
       </c>
       <c r="E16" s="4">
-        <v>46155</v>
+        <v>46162</v>
       </c>
       <c r="F16" s="4">
-        <v>46161</v>
+        <v>46176</v>
       </c>
       <c r="G16">
         <v>-17</v>
       </c>
       <c r="H16">
-        <v>-17</v>
+        <v>-12</v>
       </c>
       <c r="I16">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J16" s="1">
         <v>0</v>
@@ -1378,16 +1379,16 @@
         <v>43</v>
       </c>
       <c r="C17" s="4">
-        <v>46188</v>
+        <v>46202</v>
       </c>
       <c r="D17" s="4">
-        <v>46199</v>
+        <v>46206</v>
       </c>
       <c r="E17" s="4">
-        <v>46162</v>
+        <v>46177</v>
       </c>
       <c r="F17" s="4">
-        <v>46176</v>
+        <v>46183</v>
       </c>
       <c r="G17">
         <v>-17</v>
@@ -1396,7 +1397,7 @@
         <v>-12</v>
       </c>
       <c r="I17">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J17" s="1">
         <v>0</v>
@@ -1410,28 +1411,25 @@
         <v>45</v>
       </c>
       <c r="C18" s="4">
-        <v>46202</v>
+        <v>46111</v>
       </c>
       <c r="D18" s="4">
-        <v>46206</v>
+        <v>46114</v>
       </c>
       <c r="E18" s="4">
-        <v>46177</v>
+        <v>46111</v>
       </c>
       <c r="F18" s="4">
-        <v>46183</v>
+        <v>46114</v>
       </c>
       <c r="G18">
-        <v>-17</v>
-      </c>
-      <c r="H18">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="I18">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J18" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -1442,16 +1440,16 @@
         <v>47</v>
       </c>
       <c r="C19" s="4">
-        <v>46111</v>
+        <v>46119</v>
       </c>
       <c r="D19" s="4">
-        <v>46114</v>
+        <v>46125</v>
       </c>
       <c r="E19" s="4">
-        <v>46111</v>
+        <v>46119</v>
       </c>
       <c r="F19" s="4">
-        <v>46114</v>
+        <v>46125</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -1471,16 +1469,16 @@
         <v>49</v>
       </c>
       <c r="C20" s="4">
-        <v>46119</v>
+        <v>46126</v>
       </c>
       <c r="D20" s="4">
-        <v>46125</v>
+        <v>46132</v>
       </c>
       <c r="E20" s="4">
-        <v>46119</v>
+        <v>46126</v>
       </c>
       <c r="F20" s="4">
-        <v>46125</v>
+        <v>46132</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -1500,19 +1498,19 @@
         <v>51</v>
       </c>
       <c r="C21" s="4">
-        <v>46126</v>
+        <v>46133</v>
       </c>
       <c r="D21" s="4">
-        <v>46132</v>
+        <v>46164</v>
       </c>
       <c r="E21" s="4">
-        <v>46126</v>
+        <v>46133</v>
       </c>
       <c r="F21" s="4">
-        <v>46132</v>
+        <v>46150</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -1529,25 +1527,28 @@
         <v>53</v>
       </c>
       <c r="C22" s="4">
-        <v>46133</v>
+        <v>46168</v>
       </c>
       <c r="D22" s="4">
-        <v>46164</v>
+        <v>46174</v>
       </c>
       <c r="E22" s="4">
-        <v>46133</v>
+        <v>46153</v>
       </c>
       <c r="F22" s="4">
-        <v>46150</v>
+        <v>46157</v>
       </c>
       <c r="G22">
         <v>-10</v>
       </c>
+      <c r="H22">
+        <v>2</v>
+      </c>
       <c r="I22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" s="1">
-        <v>1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -1558,28 +1559,28 @@
         <v>55</v>
       </c>
       <c r="C23" s="4">
-        <v>46168</v>
+        <v>46188</v>
       </c>
       <c r="D23" s="4">
-        <v>46174</v>
+        <v>46199</v>
       </c>
       <c r="E23" s="4">
-        <v>46153</v>
+        <v>46162</v>
       </c>
       <c r="F23" s="4">
-        <v>46157</v>
+        <v>46176</v>
       </c>
       <c r="G23">
-        <v>-10</v>
+        <v>-17</v>
       </c>
       <c r="H23">
-        <v>2</v>
+        <v>-17</v>
       </c>
       <c r="I23">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J23" s="1">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -1590,28 +1591,25 @@
         <v>57</v>
       </c>
       <c r="C24" s="4">
-        <v>46188</v>
+        <v>46111</v>
       </c>
       <c r="D24" s="4">
-        <v>46199</v>
+        <v>46122</v>
       </c>
       <c r="E24" s="4">
-        <v>46162</v>
+        <v>46111</v>
       </c>
       <c r="F24" s="4">
-        <v>46176</v>
+        <v>46122</v>
       </c>
       <c r="G24">
-        <v>-17</v>
-      </c>
-      <c r="H24">
-        <v>-17</v>
+        <v>0</v>
       </c>
       <c r="I24">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J24" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -1622,16 +1620,16 @@
         <v>59</v>
       </c>
       <c r="C25" s="4">
-        <v>46111</v>
+        <v>46125</v>
       </c>
       <c r="D25" s="4">
-        <v>46122</v>
+        <v>46136</v>
       </c>
       <c r="E25" s="4">
-        <v>46111</v>
+        <v>46125</v>
       </c>
       <c r="F25" s="4">
-        <v>46122</v>
+        <v>46136</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -1651,19 +1649,19 @@
         <v>61</v>
       </c>
       <c r="C26" s="4">
-        <v>46125</v>
+        <v>46139</v>
       </c>
       <c r="D26" s="4">
-        <v>46136</v>
+        <v>46164</v>
       </c>
       <c r="E26" s="4">
-        <v>46125</v>
+        <v>46139</v>
       </c>
       <c r="F26" s="4">
-        <v>46136</v>
+        <v>46153</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -1680,19 +1678,19 @@
         <v>63</v>
       </c>
       <c r="C27" s="4">
-        <v>46139</v>
+        <v>46104</v>
       </c>
       <c r="D27" s="4">
-        <v>46164</v>
+        <v>46129</v>
       </c>
       <c r="E27" s="4">
-        <v>46139</v>
+        <v>46104</v>
       </c>
       <c r="F27" s="4">
-        <v>46153</v>
+        <v>46129</v>
       </c>
       <c r="G27">
-        <v>-9</v>
+        <v>0</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -1709,13 +1707,13 @@
         <v>65</v>
       </c>
       <c r="C28" s="4">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="D28" s="4">
         <v>46129</v>
       </c>
       <c r="E28" s="4">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="F28" s="4">
         <v>46129</v>
@@ -1738,16 +1736,16 @@
         <v>67</v>
       </c>
       <c r="C29" s="4">
-        <v>46111</v>
+        <v>46132</v>
       </c>
       <c r="D29" s="4">
-        <v>46129</v>
+        <v>46136</v>
       </c>
       <c r="E29" s="4">
-        <v>46111</v>
+        <v>46132</v>
       </c>
       <c r="F29" s="4">
-        <v>46129</v>
+        <v>46136</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -1761,88 +1759,92 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B30" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C30" s="4">
-        <v>46132</v>
+        <v>46202</v>
       </c>
       <c r="D30" s="4">
-        <v>46136</v>
+        <v>46213</v>
       </c>
       <c r="E30" s="4">
-        <v>46132</v>
+        <v>46177</v>
       </c>
       <c r="F30" s="4">
-        <v>46136</v>
+        <v>46190</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>-17</v>
+      </c>
+      <c r="H30">
+        <v>-17</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J30" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B31" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C31" s="4">
-        <v>46202</v>
-      </c>
-      <c r="D31" s="4"/>
+        <v>46097</v>
+      </c>
+      <c r="D31" s="4">
+        <v>46101</v>
+      </c>
       <c r="E31" s="4">
-        <v>46177</v>
-      </c>
-      <c r="F31" s="4"/>
+        <v>46097</v>
+      </c>
+      <c r="F31" s="4">
+        <v>46101</v>
+      </c>
       <c r="G31">
-        <v>-17</v>
-      </c>
-      <c r="H31">
-        <v>-17</v>
+        <v>0</v>
       </c>
       <c r="I31">
         <v>0</v>
       </c>
       <c r="J31" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B32" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C32" s="4">
-        <v>46202</v>
+        <v>46188</v>
       </c>
       <c r="D32" s="4">
-        <v>46213</v>
+        <v>46192</v>
       </c>
       <c r="E32" s="4">
-        <v>46177</v>
+        <v>46162</v>
       </c>
       <c r="F32" s="4">
-        <v>46190</v>
+        <v>46169</v>
       </c>
       <c r="G32">
         <v>-17</v>
       </c>
       <c r="H32">
-        <v>-17</v>
+        <v>21</v>
       </c>
       <c r="I32">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J32" s="1">
         <v>0</v>
@@ -1850,60 +1852,63 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B33" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C33" s="4">
-        <v>46097</v>
+        <v>46195</v>
       </c>
       <c r="D33" s="4">
-        <v>46101</v>
+        <v>46206</v>
       </c>
       <c r="E33" s="4">
-        <v>46097</v>
+        <v>46170</v>
       </c>
       <c r="F33" s="4">
-        <v>46101</v>
+        <v>46183</v>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>-17</v>
+      </c>
+      <c r="H33">
+        <v>21</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J33" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B34" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C34" s="4">
-        <v>46188</v>
+        <v>46216</v>
       </c>
       <c r="D34" s="4">
-        <v>46192</v>
+        <v>46227</v>
       </c>
       <c r="E34" s="4">
-        <v>46162</v>
+        <v>46191</v>
       </c>
       <c r="F34" s="4">
-        <v>46169</v>
+        <v>46204</v>
       </c>
       <c r="G34">
         <v>-17</v>
       </c>
       <c r="H34">
-        <v>21</v>
+        <v>-17</v>
       </c>
       <c r="I34">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J34" s="1">
         <v>0</v>
@@ -1911,31 +1916,31 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B35" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C35" s="4">
-        <v>46195</v>
+        <v>46230</v>
       </c>
       <c r="D35" s="4">
-        <v>46206</v>
+        <v>46234</v>
       </c>
       <c r="E35" s="4">
-        <v>46170</v>
+        <v>46205</v>
       </c>
       <c r="F35" s="4">
-        <v>46183</v>
+        <v>46211</v>
       </c>
       <c r="G35">
         <v>-17</v>
       </c>
       <c r="H35">
-        <v>21</v>
+        <v>-17</v>
       </c>
       <c r="I35">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J35" s="1">
         <v>0</v>
@@ -1943,22 +1948,22 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B36" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C36" s="4">
-        <v>46216</v>
+        <v>46237</v>
       </c>
       <c r="D36" s="4">
-        <v>46227</v>
+        <v>46248</v>
       </c>
       <c r="E36" s="4">
-        <v>46191</v>
+        <v>46212</v>
       </c>
       <c r="F36" s="4">
-        <v>46204</v>
+        <v>46225</v>
       </c>
       <c r="G36">
         <v>-17</v>
@@ -1975,22 +1980,22 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B37" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C37" s="4">
-        <v>46230</v>
+        <v>46251</v>
       </c>
       <c r="D37" s="4">
-        <v>46234</v>
+        <v>46255</v>
       </c>
       <c r="E37" s="4">
-        <v>46205</v>
+        <v>46226</v>
       </c>
       <c r="F37" s="4">
-        <v>46211</v>
+        <v>46232</v>
       </c>
       <c r="G37">
         <v>-17</v>
@@ -2007,31 +2012,31 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B38" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C38" s="4">
-        <v>46237</v>
+        <v>46216</v>
       </c>
       <c r="D38" s="4">
-        <v>46248</v>
+        <v>46224</v>
       </c>
       <c r="E38" s="4">
-        <v>46212</v>
+        <v>46191</v>
       </c>
       <c r="F38" s="4">
-        <v>46225</v>
+        <v>46199</v>
       </c>
       <c r="G38">
         <v>-17</v>
       </c>
       <c r="H38">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="I38">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J38" s="1">
         <v>0</v>
@@ -2039,28 +2044,28 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B39" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C39" s="4">
-        <v>46251</v>
+        <v>46225</v>
       </c>
       <c r="D39" s="4">
-        <v>46255</v>
+        <v>46231</v>
       </c>
       <c r="E39" s="4">
-        <v>46226</v>
+        <v>46202</v>
       </c>
       <c r="F39" s="4">
-        <v>46232</v>
+        <v>46206</v>
       </c>
       <c r="G39">
         <v>-17</v>
       </c>
       <c r="H39">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="I39">
         <v>5</v>
@@ -2071,22 +2076,22 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B40" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C40" s="4">
-        <v>46216</v>
+        <v>46232</v>
       </c>
       <c r="D40" s="4">
-        <v>46224</v>
+        <v>46238</v>
       </c>
       <c r="E40" s="4">
-        <v>46191</v>
+        <v>46209</v>
       </c>
       <c r="F40" s="4">
-        <v>46199</v>
+        <v>46213</v>
       </c>
       <c r="G40">
         <v>-17</v>
@@ -2095,7 +2100,7 @@
         <v>-16</v>
       </c>
       <c r="I40">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J40" s="1">
         <v>0</v>
@@ -2103,22 +2108,22 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B41" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C41" s="4">
-        <v>46225</v>
+        <v>46239</v>
       </c>
       <c r="D41" s="4">
-        <v>46231</v>
+        <v>46245</v>
       </c>
       <c r="E41" s="4">
-        <v>46202</v>
+        <v>46216</v>
       </c>
       <c r="F41" s="4">
-        <v>46206</v>
+        <v>46220</v>
       </c>
       <c r="G41">
         <v>-17</v>
@@ -2135,22 +2140,22 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B42" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C42" s="4">
-        <v>46232</v>
+        <v>46246</v>
       </c>
       <c r="D42" s="4">
-        <v>46238</v>
+        <v>46252</v>
       </c>
       <c r="E42" s="4">
-        <v>46209</v>
+        <v>46223</v>
       </c>
       <c r="F42" s="4">
-        <v>46213</v>
+        <v>46227</v>
       </c>
       <c r="G42">
         <v>-17</v>
@@ -2167,22 +2172,22 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B43" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C43" s="4">
-        <v>46239</v>
+        <v>46253</v>
       </c>
       <c r="D43" s="4">
-        <v>46245</v>
+        <v>46259</v>
       </c>
       <c r="E43" s="4">
-        <v>46216</v>
+        <v>46230</v>
       </c>
       <c r="F43" s="4">
-        <v>46220</v>
+        <v>46234</v>
       </c>
       <c r="G43">
         <v>-17</v>
@@ -2199,28 +2204,28 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B44" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C44" s="4">
-        <v>46246</v>
+        <v>46216</v>
       </c>
       <c r="D44" s="4">
-        <v>46252</v>
+        <v>46220</v>
       </c>
       <c r="E44" s="4">
-        <v>46223</v>
+        <v>46191</v>
       </c>
       <c r="F44" s="4">
-        <v>46227</v>
+        <v>46197</v>
       </c>
       <c r="G44">
         <v>-17</v>
       </c>
       <c r="H44">
-        <v>-16</v>
+        <v>11</v>
       </c>
       <c r="I44">
         <v>5</v>
@@ -2231,31 +2236,31 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B45" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C45" s="4">
-        <v>46253</v>
+        <v>46258</v>
       </c>
       <c r="D45" s="4">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="E45" s="4">
-        <v>46230</v>
+        <v>46233</v>
       </c>
       <c r="F45" s="4">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="G45">
         <v>-17</v>
       </c>
       <c r="H45">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="I45">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J45" s="1">
         <v>0</v>
@@ -2263,28 +2268,28 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B46" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C46" s="4">
-        <v>46216</v>
+        <v>46237</v>
       </c>
       <c r="D46" s="4">
-        <v>46220</v>
+        <v>46241</v>
       </c>
       <c r="E46" s="4">
-        <v>46191</v>
+        <v>46212</v>
       </c>
       <c r="F46" s="4">
-        <v>46197</v>
+        <v>46218</v>
       </c>
       <c r="G46">
         <v>-17</v>
       </c>
       <c r="H46">
-        <v>11</v>
+        <v>-4</v>
       </c>
       <c r="I46">
         <v>5</v>
@@ -2295,31 +2300,31 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B47" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C47" s="4">
-        <v>46258</v>
+        <v>46174</v>
       </c>
       <c r="D47" s="4">
-        <v>46260</v>
+        <v>46174</v>
       </c>
       <c r="E47" s="4">
-        <v>46233</v>
+        <v>46154</v>
       </c>
       <c r="F47" s="4">
-        <v>46237</v>
+        <v>46154</v>
       </c>
       <c r="G47">
-        <v>-17</v>
+        <v>-12</v>
       </c>
       <c r="H47">
-        <v>-17</v>
+        <v>38</v>
       </c>
       <c r="I47">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J47" s="1">
         <v>0</v>
@@ -2327,31 +2332,31 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B48" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C48" s="4">
-        <v>46237</v>
+        <v>46174</v>
       </c>
       <c r="D48" s="4">
-        <v>46241</v>
+        <v>46183</v>
       </c>
       <c r="E48" s="4">
-        <v>46212</v>
+        <v>46155</v>
       </c>
       <c r="F48" s="4">
-        <v>46218</v>
+        <v>46169</v>
       </c>
       <c r="G48">
-        <v>-17</v>
+        <v>-10</v>
       </c>
       <c r="H48">
-        <v>-4</v>
+        <v>38</v>
       </c>
       <c r="I48">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J48" s="1">
         <v>0</v>
@@ -2359,31 +2364,31 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B49" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C49" s="4">
-        <v>46174</v>
+        <v>46216</v>
       </c>
       <c r="D49" s="4">
-        <v>46174</v>
+        <v>46227</v>
       </c>
       <c r="E49" s="4">
-        <v>46154</v>
+        <v>46191</v>
       </c>
       <c r="F49" s="4">
-        <v>46154</v>
+        <v>46204</v>
       </c>
       <c r="G49">
-        <v>-12</v>
+        <v>-17</v>
       </c>
       <c r="H49">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="I49">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J49" s="1">
         <v>0</v>
@@ -2391,31 +2396,31 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B50" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C50" s="4">
-        <v>46174</v>
+        <v>46237</v>
       </c>
       <c r="D50" s="4">
-        <v>46183</v>
+        <v>46241</v>
       </c>
       <c r="E50" s="4">
-        <v>46155</v>
+        <v>46212</v>
       </c>
       <c r="F50" s="4">
-        <v>46169</v>
+        <v>46218</v>
       </c>
       <c r="G50">
-        <v>-10</v>
+        <v>-17</v>
       </c>
       <c r="H50">
-        <v>38</v>
+        <v>-4</v>
       </c>
       <c r="I50">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J50" s="1">
         <v>0</v>
@@ -2423,31 +2428,31 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B51" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C51" s="4">
-        <v>46216</v>
+        <v>46237</v>
       </c>
       <c r="D51" s="4">
-        <v>46227</v>
+        <v>46241</v>
       </c>
       <c r="E51" s="4">
-        <v>46191</v>
+        <v>46212</v>
       </c>
       <c r="F51" s="4">
-        <v>46204</v>
+        <v>46218</v>
       </c>
       <c r="G51">
         <v>-17</v>
       </c>
       <c r="H51">
-        <v>6</v>
+        <v>-4</v>
       </c>
       <c r="I51">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J51" s="1">
         <v>0</v>
@@ -2455,31 +2460,31 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B52" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C52" s="4">
-        <v>46237</v>
+        <v>46216</v>
       </c>
       <c r="D52" s="4">
-        <v>46241</v>
+        <v>46218</v>
       </c>
       <c r="E52" s="4">
-        <v>46212</v>
+        <v>46191</v>
       </c>
       <c r="F52" s="4">
-        <v>46218</v>
+        <v>46195</v>
       </c>
       <c r="G52">
         <v>-17</v>
       </c>
       <c r="H52">
-        <v>-4</v>
+        <v>-11</v>
       </c>
       <c r="I52">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J52" s="1">
         <v>0</v>
@@ -2487,31 +2492,31 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B53" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C53" s="4">
-        <v>46237</v>
+        <v>46219</v>
       </c>
       <c r="D53" s="4">
-        <v>46241</v>
+        <v>46223</v>
       </c>
       <c r="E53" s="4">
-        <v>46212</v>
+        <v>46196</v>
       </c>
       <c r="F53" s="4">
-        <v>46218</v>
+        <v>46198</v>
       </c>
       <c r="G53">
         <v>-17</v>
       </c>
       <c r="H53">
-        <v>-4</v>
+        <v>-11</v>
       </c>
       <c r="I53">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J53" s="1">
         <v>0</v>
@@ -2519,22 +2524,22 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B54" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C54" s="4">
-        <v>46216</v>
+        <v>46224</v>
       </c>
       <c r="D54" s="4">
-        <v>46218</v>
+        <v>46226</v>
       </c>
       <c r="E54" s="4">
-        <v>46191</v>
+        <v>46199</v>
       </c>
       <c r="F54" s="4">
-        <v>46195</v>
+        <v>46203</v>
       </c>
       <c r="G54">
         <v>-17</v>
@@ -2551,22 +2556,22 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B55" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C55" s="4">
-        <v>46219</v>
+        <v>46227</v>
       </c>
       <c r="D55" s="4">
-        <v>46223</v>
+        <v>46231</v>
       </c>
       <c r="E55" s="4">
-        <v>46196</v>
+        <v>46204</v>
       </c>
       <c r="F55" s="4">
-        <v>46198</v>
+        <v>46206</v>
       </c>
       <c r="G55">
         <v>-17</v>
@@ -2583,22 +2588,22 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C56" s="4">
-        <v>46224</v>
+        <v>46232</v>
       </c>
       <c r="D56" s="4">
-        <v>46226</v>
+        <v>46245</v>
       </c>
       <c r="E56" s="4">
-        <v>46199</v>
+        <v>46209</v>
       </c>
       <c r="F56" s="4">
-        <v>46203</v>
+        <v>46220</v>
       </c>
       <c r="G56">
         <v>-17</v>
@@ -2607,7 +2612,7 @@
         <v>-11</v>
       </c>
       <c r="I56">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J56" s="1">
         <v>0</v>
@@ -2615,28 +2620,28 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B57" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C57" s="4">
-        <v>46227</v>
+        <v>46232</v>
       </c>
       <c r="D57" s="4">
-        <v>46231</v>
+        <v>46234</v>
       </c>
       <c r="E57" s="4">
-        <v>46204</v>
+        <v>46209</v>
       </c>
       <c r="F57" s="4">
-        <v>46206</v>
+        <v>46211</v>
       </c>
       <c r="G57">
         <v>-17</v>
       </c>
       <c r="H57">
-        <v>-11</v>
+        <v>-4</v>
       </c>
       <c r="I57">
         <v>3</v>
@@ -2647,144 +2652,144 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B58" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C58" s="4">
-        <v>46232</v>
+        <v>46160</v>
       </c>
       <c r="D58" s="4">
-        <v>46245</v>
+        <v>46168</v>
       </c>
       <c r="E58" s="4">
-        <v>46209</v>
+        <v>46139</v>
       </c>
       <c r="F58" s="4">
-        <v>46220</v>
+        <v>46153</v>
       </c>
       <c r="G58">
-        <v>-17</v>
-      </c>
-      <c r="H58">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="I58">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J58" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B59" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C59" s="4">
-        <v>46232</v>
+        <v>46168</v>
       </c>
       <c r="D59" s="4">
-        <v>46234</v>
+        <v>46170</v>
       </c>
       <c r="E59" s="4">
-        <v>46209</v>
+        <v>46154</v>
       </c>
       <c r="F59" s="4">
-        <v>46211</v>
+        <v>46156</v>
       </c>
       <c r="G59">
-        <v>-17</v>
-      </c>
-      <c r="H59">
-        <v>-4</v>
+        <v>-9</v>
       </c>
       <c r="I59">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J59" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B60" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C60" s="4">
+        <v>46169</v>
+      </c>
+      <c r="D60" s="4">
+        <v>46175</v>
+      </c>
+      <c r="E60" s="4">
+        <v>46154</v>
+      </c>
+      <c r="F60" s="4">
         <v>46160</v>
-      </c>
-      <c r="D60" s="4">
-        <v>46168</v>
-      </c>
-      <c r="E60" s="4">
-        <v>46139</v>
-      </c>
-      <c r="F60" s="4">
-        <v>46153</v>
       </c>
       <c r="G60">
         <v>-10</v>
       </c>
+      <c r="H60">
+        <v>31</v>
+      </c>
       <c r="I60">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J60" s="1">
-        <v>1</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B61" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C61" s="4">
-        <v>46168</v>
+        <v>46171</v>
       </c>
       <c r="D61" s="4">
-        <v>46170</v>
+        <v>46184</v>
       </c>
       <c r="E61" s="4">
-        <v>46154</v>
+        <v>46157</v>
       </c>
       <c r="F61" s="4">
-        <v>46156</v>
+        <v>46171</v>
       </c>
       <c r="G61">
         <v>-9</v>
       </c>
+      <c r="H61">
+        <v>22</v>
+      </c>
       <c r="I61">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J61" s="1">
-        <v>1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B62" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C62" s="4">
-        <v>46169</v>
+        <v>46176</v>
       </c>
       <c r="D62" s="4">
-        <v>46175</v>
+        <v>46178</v>
       </c>
       <c r="E62" s="4">
-        <v>46154</v>
+        <v>46161</v>
       </c>
       <c r="F62" s="4">
-        <v>46160</v>
+        <v>46163</v>
       </c>
       <c r="G62">
         <v>-10</v>
@@ -2793,30 +2798,30 @@
         <v>31</v>
       </c>
       <c r="I62">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J62" s="1">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B63" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C63" s="4">
-        <v>46171</v>
+        <v>46185</v>
       </c>
       <c r="D63" s="4">
-        <v>46184</v>
+        <v>46198</v>
       </c>
       <c r="E63" s="4">
-        <v>46157</v>
+        <v>46174</v>
       </c>
       <c r="F63" s="4">
-        <v>46171</v>
+        <v>46185</v>
       </c>
       <c r="G63">
         <v>-9</v>
@@ -2825,39 +2830,39 @@
         <v>22</v>
       </c>
       <c r="I63">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J63" s="1">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B64" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C64" s="4">
-        <v>46176</v>
+        <v>46199</v>
       </c>
       <c r="D64" s="4">
-        <v>46178</v>
+        <v>46205</v>
       </c>
       <c r="E64" s="4">
-        <v>46161</v>
+        <v>46188</v>
       </c>
       <c r="F64" s="4">
-        <v>46163</v>
+        <v>46192</v>
       </c>
       <c r="G64">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="H64">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I64">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J64" s="1">
         <v>0</v>
@@ -2865,60 +2870,60 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B65" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C65" s="4">
-        <v>46185</v>
+        <v>46171</v>
       </c>
       <c r="D65" s="4">
-        <v>46198</v>
+        <v>46177</v>
       </c>
       <c r="E65" s="4">
-        <v>46174</v>
+        <v>46157</v>
       </c>
       <c r="F65" s="4">
-        <v>46185</v>
+        <v>46163</v>
       </c>
       <c r="G65">
         <v>-9</v>
       </c>
       <c r="H65">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I65">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J65" s="1">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B66" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C66" s="4">
-        <v>46199</v>
+        <v>46181</v>
       </c>
       <c r="D66" s="4">
-        <v>46205</v>
+        <v>46185</v>
       </c>
       <c r="E66" s="4">
-        <v>46188</v>
+        <v>46164</v>
       </c>
       <c r="F66" s="4">
-        <v>46192</v>
+        <v>46171</v>
       </c>
       <c r="G66">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H66">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="I66">
         <v>5</v>
@@ -2929,34 +2934,30 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B67" t="s">
-        <v>143</v>
+        <v>68</v>
       </c>
       <c r="C67" s="4">
-        <v>46171</v>
-      </c>
-      <c r="D67" s="4">
-        <v>46177</v>
-      </c>
+        <v>46261</v>
+      </c>
+      <c r="D67" s="4"/>
       <c r="E67" s="4">
-        <v>46157</v>
-      </c>
-      <c r="F67" s="4">
-        <v>46163</v>
-      </c>
+        <v>46238</v>
+      </c>
+      <c r="F67" s="4"/>
       <c r="G67">
-        <v>-9</v>
+        <v>-17</v>
       </c>
       <c r="H67">
-        <v>32</v>
+        <v>-17</v>
       </c>
       <c r="I67">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J67" s="1">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
@@ -2964,28 +2965,28 @@
         <v>144</v>
       </c>
       <c r="B68" t="s">
-        <v>145</v>
+        <v>70</v>
       </c>
       <c r="C68" s="4">
-        <v>46181</v>
+        <v>46261</v>
       </c>
       <c r="D68" s="4">
-        <v>46185</v>
+        <v>46275</v>
       </c>
       <c r="E68" s="4">
-        <v>46164</v>
+        <v>46238</v>
       </c>
       <c r="F68" s="4">
-        <v>46171</v>
+        <v>46251</v>
       </c>
       <c r="G68">
-        <v>-10</v>
+        <v>-17</v>
       </c>
       <c r="H68">
-        <v>31</v>
+        <v>-17</v>
       </c>
       <c r="I68">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J68" s="1">
         <v>0</v>
@@ -2993,19 +2994,23 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
+        <v>145</v>
+      </c>
+      <c r="B69" t="s">
         <v>146</v>
       </c>
-      <c r="B69" t="s">
-        <v>71</v>
-      </c>
       <c r="C69" s="4">
-        <v>46261</v>
-      </c>
-      <c r="D69" s="4"/>
+        <v>46276</v>
+      </c>
+      <c r="D69" s="4">
+        <v>46289</v>
+      </c>
       <c r="E69" s="4">
-        <v>46238</v>
-      </c>
-      <c r="F69" s="4"/>
+        <v>46252</v>
+      </c>
+      <c r="F69" s="4">
+        <v>46266</v>
+      </c>
       <c r="G69">
         <v>-17</v>
       </c>
@@ -3013,7 +3018,7 @@
         <v>-17</v>
       </c>
       <c r="I69">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J69" s="1">
         <v>0</v>
@@ -3024,19 +3029,15 @@
         <v>147</v>
       </c>
       <c r="B70" t="s">
-        <v>73</v>
-      </c>
-      <c r="C70" s="4">
-        <v>46261</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="C70" s="4"/>
       <c r="D70" s="4">
-        <v>46275</v>
-      </c>
-      <c r="E70" s="4">
-        <v>46238</v>
-      </c>
+        <v>46289</v>
+      </c>
+      <c r="E70" s="4"/>
       <c r="F70" s="4">
-        <v>46251</v>
+        <v>46266</v>
       </c>
       <c r="G70">
         <v>-17</v>
@@ -3045,69 +3046,9 @@
         <v>-17</v>
       </c>
       <c r="I70">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J70" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>148</v>
-      </c>
-      <c r="B71" t="s">
-        <v>149</v>
-      </c>
-      <c r="C71" s="4">
-        <v>46276</v>
-      </c>
-      <c r="D71" s="4">
-        <v>46289</v>
-      </c>
-      <c r="E71" s="4">
-        <v>46252</v>
-      </c>
-      <c r="F71" s="4">
-        <v>46266</v>
-      </c>
-      <c r="G71">
-        <v>-17</v>
-      </c>
-      <c r="H71">
-        <v>-17</v>
-      </c>
-      <c r="I71">
-        <v>10</v>
-      </c>
-      <c r="J71" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>150</v>
-      </c>
-      <c r="B72" t="s">
-        <v>151</v>
-      </c>
-      <c r="C72" s="4"/>
-      <c r="D72" s="4">
-        <v>46289</v>
-      </c>
-      <c r="E72" s="4"/>
-      <c r="F72" s="4">
-        <v>46266</v>
-      </c>
-      <c r="G72">
-        <v>-17</v>
-      </c>
-      <c r="H72">
-        <v>-17</v>
-      </c>
-      <c r="I72">
-        <v>0</v>
-      </c>
-      <c r="J72" s="1">
         <v>0</v>
       </c>
     </row>
